--- a/UKMLA_Internal_Linking_Map.xlsx
+++ b/UKMLA_Internal_Linking_Map.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -526,14 +526,14 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -561,14 +561,14 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -596,14 +596,14 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -631,14 +631,14 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -666,14 +666,14 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -701,14 +701,14 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -736,14 +736,14 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -771,14 +771,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -806,14 +806,14 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -841,14 +841,14 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -876,14 +876,14 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -911,14 +911,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -946,14 +946,14 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -981,14 +981,14 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>16</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1024,14 +1024,14 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>10</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1067,14 +1067,14 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1110,14 +1110,14 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>13</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1153,14 +1153,14 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1282,14 +1282,14 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>12</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1325,14 +1325,14 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1368,14 +1368,14 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>20</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1561,12 +1561,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-read-akt-stem</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1575,41 +1575,41 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-register-plab-1</t>
+          <t>/news#how-to-read-akt-stem</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1618,41 +1618,41 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
+          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>/news#infection-microbiology-ukmla-revision</t>
+          <t>/news#how-to-register-plab-1</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1661,41 +1661,41 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
+          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>/news#mental-health-ukmla-revision</t>
+          <t>/news#infection-microbiology-ukmla-revision</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1704,19 +1704,19 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1733,12 +1733,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>/news#mla-content-map-explained</t>
+          <t>/news#mental-health-ukmla-revision</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1747,24 +1747,24 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>The Role of Mock Exams in UKMLA Preparation</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>/news#mock-exams-ukmla-preparation</t>
+          <t>/news#mla-content-map-explained</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1790,41 +1790,41 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
+          <t>The Role of Mock Exams in UKMLA Preparation</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>/news#nephrology-ukmla-revision</t>
+          <t>/news#mock-exams-ukmla-preparation</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1833,41 +1833,41 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
+          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>/news#neurology-ukmla-revision</t>
+          <t>/news#nephrology-ukmla-revision</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1876,19 +1876,19 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
+          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>/news#nice-guidelines-akt-revision</t>
+          <t>/news#neurology-ukmla-revision</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1919,19 +1919,19 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
+          <t>/news#nice-guidelines-akt-revision</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1962,19 +1962,19 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1991,12 +1991,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
+          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>/news#ophthalmology-ent-ukmla-revision</t>
+          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2005,19 +2005,19 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>/news#paediatrics-ukmla-revision</t>
+          <t>/news#ophthalmology-ent-ukmla-revision</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2048,19 +2048,19 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
+          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>/news#palliative-care-ukmla-revision</t>
+          <t>/news#paediatrics-ukmla-revision</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#palliative-care-ukmla-revision</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2134,37 +2134,41 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr"/>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>/news#plab-2-preparation-guide</t>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2173,41 +2177,37 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>UKMLA vs PLAB</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>/news#psychiatry-communication-cpsa-stations</t>
+          <t>/news#plab-2-preparation-guide</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2216,41 +2216,41 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Radiology and Imaging Interpretation in the AKT</t>
+          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>/news#radiology-imaging-akt-ukmla</t>
+          <t>/news#psychiatry-communication-cpsa-stations</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2262,38 +2262,38 @@
         <v>16</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Radiology and Imaging Interpretation in the AKT</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>/news#respiratory-medicine-ukmla-revision</t>
+          <t>/news#radiology-imaging-akt-ukmla</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2302,19 +2302,19 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
+          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>/news#rheumatology-ukmla-revision</t>
+          <t>/news#respiratory-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2345,19 +2345,19 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>/news#safeguarding-ukmla-revision</t>
+          <t>/news#rheumatology-ukmla-revision</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2391,34 +2391,38 @@
         <v>7</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>/news#social-determinants-health-ukmla</t>
+          <t>/news#safeguarding-ukmla-revision</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2427,41 +2431,37 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Fees: The Complete 2026 Cost Breakdown; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>/news#surgical-presentations-ukmla-revision</t>
+          <t>/news#social-determinants-health-ukmla</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2470,19 +2470,19 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>/news#three-months-ukmla-akt-countdown</t>
+          <t>/news#surgical-presentations-ukmla-revision</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2513,41 +2513,41 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>/news#time-management-akt-ukmla</t>
+          <t>/news#three-months-ukmla-akt-countdown</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2556,19 +2556,19 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-medical-schools-ukmla-implementation</t>
+          <t>/news#time-management-akt-ukmla</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2599,41 +2599,41 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA?</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-format-preparation</t>
+          <t>/news#uk-medical-schools-ukmla-implementation</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2642,41 +2642,41 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-cpsa-what-it-tests</t>
+          <t>/news#ukmla-akt-format-preparation</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2685,19 +2685,19 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2707,19 +2707,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
+          <t>/news#ukmla-cpsa-what-it-tests</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2728,41 +2728,41 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-explained</t>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2771,19 +2771,19 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2793,19 +2793,19 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-graduate-entry-medical-students</t>
+          <t>/news#ukmla-fees-explained</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2814,41 +2814,41 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-key-dates-sitting-schedule</t>
+          <t>/news#ukmla-fees-for-img-2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2857,19 +2857,19 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Fees; Official Resources; Preparation; Results and Scoring; UKMLA vs PLAB; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2879,19 +2879,19 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Key Dates</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-preparation-for-imgs</t>
+          <t>/news#ukmla-for-nigerian-doctors</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2900,41 +2900,41 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-resits-rules-limits</t>
+          <t>/news#ukmla-for-pakistani-doctors</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2946,38 +2946,38 @@
         <v>2</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Fees; Preparation; Results and Scoring; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-results-feedback-report</t>
+          <t>/news#ukmla-graduate-entry-medical-students</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2986,41 +2986,41 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>31</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Appeals and Resits; Eligibility; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-revision-notes-strategy</t>
+          <t>/news#ukmla-key-dates-sitting-schedule</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3029,41 +3029,41 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Appeals and Resits; Eligibility; Fees; Official Resources; Preparation; Results and Scoring; UKMLA vs PLAB; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Key Dates</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB: What Is the Difference?</t>
+          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-plab-difference</t>
+          <t>/news#ukmla-preparation-for-imgs</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3072,19 +3072,19 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Appeals and Resits; Eligibility; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3101,48 +3101,349 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; Fees; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-resits-rules-limits</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Fees; Preparation; Results and Scoring; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-results-feedback-report</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-revision-notes-strategy</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Exam Preparation</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB: What Is the Difference?</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-plab-difference</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>/news#what-is-ukmla-complete-guide</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Blog Post</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E72" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>Understanding the Foundation Programme: What Awaits After the UKMLA; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Core UKMLA Overview</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I65"/>
+  <autoFilter ref="A1:I72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3179,7 +3480,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -3199,7 +3500,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>734</v>
+        <v>905</v>
       </c>
     </row>
     <row r="5">
@@ -3209,7 +3510,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="6">
@@ -3260,7 +3561,7 @@
       <c r="A12" s="5" t="inlineStr"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know (31 incoming)</t>
+          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know (33 incoming)</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3569,7 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Respiratory Medicine for the UKMLA: What to Focus On (30 incoming)</t>
+          <t>Respiratory Medicine for the UKMLA: What to Focus On (31 incoming)</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3577,7 @@
       <c r="A14" s="5" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide (27 incoming)</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview (30 incoming)</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3585,7 @@
       <c r="A15" s="5" t="inlineStr"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More (25 incoming)</t>
+          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide (28 incoming)</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3593,7 @@
       <c r="A16" s="5" t="inlineStr"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT (24 incoming)</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT (26 incoming)</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3601,7 @@
       <c r="A17" s="5" t="inlineStr"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting (24 incoming)</t>
+          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More (26 incoming)</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3609,7 @@
       <c r="A18" s="5" t="inlineStr"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview (24 incoming)</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting (25 incoming)</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3617,7 @@
       <c r="A19" s="5" t="inlineStr"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise (23 incoming)</t>
+          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide (24 incoming)</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3625,7 @@
       <c r="A20" s="5" t="inlineStr"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide (23 incoming)</t>
+          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise (23 incoming)</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3633,7 @@
       <c r="A21" s="5" t="inlineStr"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips (16 incoming)</t>
+          <t>Radiology and Imaging Interpretation in the AKT (17 incoming)</t>
         </is>
       </c>
     </row>

--- a/UKMLA_Internal_Linking_Map.xlsx
+++ b/UKMLA_Internal_Linking_Map.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -526,14 +526,14 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -561,14 +561,14 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -596,14 +596,14 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -631,14 +631,14 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -666,14 +666,14 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -701,14 +701,14 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -736,14 +736,14 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -771,14 +771,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -806,14 +806,14 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -841,14 +841,14 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -876,14 +876,14 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -911,14 +911,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -946,14 +946,14 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Read an AKT Stem: Avoiding Common Traps; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -981,14 +981,14 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>16</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1325,14 +1325,14 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1354,12 +1354,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-programme-after-ukmla</t>
+          <t>/news#english-language-requirement-for-ukmla-india</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1368,37 +1368,41 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Eligibility; Official Resources; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>/news#gastroenterology-ukmla-akt-revision</t>
+          <t>/news#foundation-programme-after-ukmla</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1407,41 +1411,37 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
+          <t>Uncategorised</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>/news#good-medical-practice-ukmla</t>
+          <t>/news#gastroenterology-ukmla-akt-revision</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1450,37 +1450,41 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>11</v>
-      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>/news#group-study-vs-solo-ukmla</t>
+          <t>/news#gmc-registration-and-epic-verification-india</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1489,41 +1493,41 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Eligibility; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>/news#haematology-ukmla-revision</t>
+          <t>/news#gmc-registration-requirements-for-international-doctors</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1532,41 +1536,41 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
+          <t>/news#good-medical-practice-ukmla</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1575,41 +1579,37 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-read-akt-stem</t>
+          <t>/news#group-study-vs-solo-ukmla</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1618,41 +1618,41 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-register-plab-1</t>
+          <t>/news#haematology-ukmla-revision</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1664,38 +1664,38 @@
         <v>4</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>/news#infection-microbiology-ukmla-revision</t>
+          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1704,41 +1704,41 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>/news#mental-health-ukmla-revision</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1747,41 +1747,41 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>/news#mla-content-map-explained</t>
+          <t>/news#how-to-read-akt-stem</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1790,41 +1790,41 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>The Role of Mock Exams in UKMLA Preparation</t>
+          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>/news#mock-exams-ukmla-preparation</t>
+          <t>/news#how-to-register-plab-1</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1833,41 +1833,41 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
+          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>/news#nephrology-ukmla-revision</t>
+          <t>/news#infection-microbiology-ukmla-revision</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1876,19 +1876,19 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>/news#neurology-ukmla-revision</t>
+          <t>/news#is-indian-mbbs-valid-in-uk</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1919,41 +1919,41 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Eligibility; Official Resources; What Is the UKMLA?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>/news#nice-guidelines-akt-revision</t>
+          <t>/news#managing-ukmla-exam-anxiety</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1962,41 +1962,41 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Preparation; What Is an Angoff Standard Setting and Why Does It Matter?; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
+          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
+          <t>/news#mbbs-in-uk-for-indian-students</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2005,41 +2005,41 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Fees; MLA Content Map / Syllabus; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>/news#ophthalmology-ent-ukmla-revision</t>
+          <t>/news#mental-health-ukmla-revision</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2048,19 +2048,19 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>/news#paediatrics-ukmla-revision</t>
+          <t>/news#mla-content-map-explained</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2091,24 +2091,24 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
+          <t>The Role of Mock Exams in UKMLA Preparation</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>/news#palliative-care-ukmla-revision</t>
+          <t>/news#mock-exams-ukmla-preparation</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2134,41 +2134,41 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#nephrology-ukmla-revision</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2177,37 +2177,41 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
+          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>/news#plab-2-preparation-guide</t>
+          <t>/news#neurology-ukmla-revision</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2216,41 +2220,41 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>/news#psychiatry-communication-cpsa-stations</t>
+          <t>/news#nice-guidelines-akt-revision</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2259,41 +2263,41 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Radiology and Imaging Interpretation in the AKT</t>
+          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>/news#radiology-imaging-akt-ukmla</t>
+          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2302,19 +2306,19 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2331,12 +2335,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>/news#respiratory-medicine-ukmla-revision</t>
+          <t>/news#ophthalmology-ent-ukmla-revision</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2345,19 +2349,19 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2374,12 +2378,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
+          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>/news#rheumatology-ukmla-revision</t>
+          <t>/news#paediatrics-ukmla-revision</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2388,19 +2392,19 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2417,12 +2421,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>/news#safeguarding-ukmla-revision</t>
+          <t>/news#palliative-care-ukmla-revision</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2431,37 +2435,41 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr"/>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>/news#social-determinants-health-ukmla</t>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2470,41 +2478,37 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>/news#surgical-presentations-ukmla-revision</t>
+          <t>/news#pharmacology-prescribing-safety-ukmla</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2513,19 +2517,19 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2542,12 +2546,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>/news#three-months-ukmla-akt-countdown</t>
+          <t>/news#plab-2-preparation-guide</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2556,41 +2560,41 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>/news#time-management-akt-ukmla</t>
+          <t>/news#psychiatry-communication-cpsa-stations</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2599,41 +2603,41 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Radiology and Imaging Interpretation in the AKT</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-medical-schools-ukmla-implementation</t>
+          <t>/news#radiology-imaging-akt-ukmla</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2642,41 +2646,41 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA?</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-format-preparation</t>
+          <t>/news#respiratory-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2685,41 +2689,41 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-cpsa-what-it-tests</t>
+          <t>/news#rheumatology-ukmla-revision</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2731,38 +2735,38 @@
         <v>7</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
+          <t>/news#safeguarding-ukmla-revision</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2771,41 +2775,37 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-explained</t>
+          <t>/news#social-determinants-health-ukmla</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2817,38 +2817,38 @@
         <v>5</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-for-img-2026</t>
+          <t>/news#surgical-presentations-ukmla-revision</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2857,41 +2857,41 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-nigerian-doctors</t>
+          <t>/news#three-months-ukmla-akt-countdown</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2900,41 +2900,41 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>24</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-pakistani-doctors</t>
+          <t>/news#time-management-akt-ukmla</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2943,41 +2943,41 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-graduate-entry-medical-students</t>
+          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2986,24 +2986,24 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Eligibility; Fees; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-key-dates-sitting-schedule</t>
+          <t>/news#uk-medical-schools-ukmla-implementation</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3029,41 +3029,41 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Fees; Official Resources; Preparation; Results and Scoring; UKMLA vs PLAB; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Key Dates</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-preparation-for-imgs</t>
+          <t>/news#uk-visa-guide-for-international-doctors</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3072,41 +3072,41 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-question-bank-and-mock-tests</t>
+          <t>/news#ukmla-akt-format-preparation</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3115,41 +3115,41 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; Fees; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-resits-rules-limits</t>
+          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3158,41 +3158,41 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Fees; Preparation; Results and Scoring; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Appeals and Resits; Results and Scoring; What Is an Angoff Standard Setting and Why Does It Matter?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Results &amp; Scoring</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Results and Scoring</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-results-feedback-report</t>
+          <t>/news#ukmla-akt-test-centres-guide</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3201,41 +3201,41 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-revision-notes-strategy</t>
+          <t>/news#ukmla-cpsa-what-it-tests</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3244,41 +3244,41 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-neet-pg</t>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3287,41 +3287,41 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-plab-difference</t>
+          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3333,38 +3333,38 @@
         <v>3</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Eligibility; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-usmle-comparison</t>
+          <t>/news#ukmla-fees-explained</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3373,77 +3373,1066 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-bangladeshi-doctors</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-egyptian-doctors</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-filipino-doctors</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-gulf-doctors</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-nigerian-doctors</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-pakistani-doctors</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-refugee-doctors</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Fees; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-south-african-doctors</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-sri-lankan-doctors</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-graduate-entry-medical-students</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-key-dates-sitting-schedule</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; Fees; Official Resources; Preparation; Results and Scoring; UKMLA vs PLAB; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-preparation-for-imgs</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; Fees; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-resits-rules-limits</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Fees; Preparation; Results and Scoring; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-results-feedback-report</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-revision-notes-strategy</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Exam Preparation</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-to-nhs-job-pathway</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; UKMLA vs PLAB; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB: What Is the Difference?</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-plab-difference</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
           <t>What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>/news#what-is-ukmla-complete-guide</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Blog Post</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" s="2" t="n">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; UKMLA AKT: Format, Question Types, and How to Prepare</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Core UKMLA Overview</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I72"/>
+  <autoFilter ref="A1:I95"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3480,7 +4469,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -3500,7 +4489,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>905</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="5">
@@ -3510,7 +4499,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="6">
@@ -3577,7 +4566,7 @@
       <c r="A14" s="5" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview (30 incoming)</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview (31 incoming)</t>
         </is>
       </c>
     </row>
@@ -3609,7 +4598,7 @@
       <c r="A18" s="5" t="inlineStr"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting (25 incoming)</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting (26 incoming)</t>
         </is>
       </c>
     </row>
@@ -3617,7 +4606,7 @@
       <c r="A19" s="5" t="inlineStr"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide (24 incoming)</t>
+          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide (25 incoming)</t>
         </is>
       </c>
     </row>
@@ -3633,7 +4622,7 @@
       <c r="A21" s="5" t="inlineStr"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Radiology and Imaging Interpretation in the AKT (17 incoming)</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route (23 incoming)</t>
         </is>
       </c>
     </row>

--- a/UKMLA_Internal_Linking_Map.xlsx
+++ b/UKMLA_Internal_Linking_Map.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -526,14 +526,14 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -561,14 +561,14 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; OET vs IELTS for GMC Registration: Which Should You Take?; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -596,14 +596,14 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -631,14 +631,14 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -666,14 +666,14 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -701,14 +701,14 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -771,14 +771,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; OET vs IELTS for GMC Registration: Which Should You Take?; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -806,14 +806,14 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Internship Requirement for GMC Registration, Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs; OET vs IELTS for GMC Registration: Which Should You Take?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; How UK Medical Schools Implement the UKMLA: An Overview; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -841,14 +841,14 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The Role of Mock Exams in UKMLA Preparation; OET vs IELTS for GMC Registration: Which Should You Take?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -876,14 +876,14 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -911,14 +911,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MLA Content Map: The Blueprint Behind Every UKMLA Question; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -946,14 +946,14 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Read an AKT Stem: Avoiding Common Traps; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Read an AKT Stem: Avoiding Common Traps; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -1368,14 +1368,14 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -1397,12 +1397,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-programme-after-ukmla</t>
+          <t>/news#foundation-programme-2026-recruitment-changes</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1411,37 +1411,41 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Regulation of Physician Associates: What Doctors Need to Know; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Eligibility; Key Dates; Preparation; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>/news#gastroenterology-ukmla-akt-revision</t>
+          <t>/news#foundation-programme-after-ukmla</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1450,41 +1454,37 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
+          <t>Uncategorised</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-and-epic-verification-india</t>
+          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1493,19 +1493,19 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1515,19 +1515,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
+          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-requirements-for-international-doctors</t>
+          <t>/news#gastroenterology-ukmla-akt-revision</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1536,41 +1536,41 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>/news#good-medical-practice-ukmla</t>
+          <t>/news#gmc-english-language-exemption-for-imgs</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1579,37 +1579,41 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>/news#group-study-vs-solo-ukmla</t>
+          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1621,38 +1625,38 @@
         <v>3</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>/news#haematology-ukmla-revision</t>
+          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1664,38 +1668,38 @@
         <v>4</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
+          <t>/news#gmc-recognised-primary-medical-qualifications</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1704,24 +1708,24 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>The Internship Requirement for GMC Registration, Explained; OET vs IELTS for GMC Registration: Which Should You Take?</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>Eligibility; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1733,12 +1737,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
+          <t>/news#gmc-registration-and-epic-verification-india</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1747,19 +1751,19 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Eligibility; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1769,19 +1773,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-read-akt-stem</t>
+          <t>/news#gmc-registration-refund-policy</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1790,41 +1794,41 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How Long Does GMC Registration Take? A Realistic Timeline; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Fees; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-register-plab-1</t>
+          <t>/news#gmc-registration-requirements-for-international-doctors</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1833,24 +1837,24 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Eligibility; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1862,12 +1866,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
+          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>/news#infection-microbiology-ukmla-revision</t>
+          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1876,41 +1880,41 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; AKT Exam Pattern; Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; Good Medical Practice and the UKMLA: What the GMC Expects; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
+          <t>The GMC Revalidation Process, Explained for New Doctors</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>/news#is-indian-mbbs-valid-in-uk</t>
+          <t>/news#gmc-revalidation-process-explained</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1919,41 +1923,41 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>11</v>
-      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; What Is the UKMLA?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
+          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>/news#managing-ukmla-exam-anxiety</t>
+          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1962,41 +1966,41 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; OET vs IELTS for GMC Registration: Which Should You Take?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Preparation; What Is an Angoff Standard Setting and Why Does It Matter?; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Preparation; Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>/news#mbbs-in-uk-for-indian-students</t>
+          <t>/news#good-medical-practice-ukmla</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2005,41 +2009,37 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; MLA Content Map / Syllabus; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>/news#mental-health-ukmla-revision</t>
+          <t>/news#group-study-vs-solo-ukmla</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2048,41 +2048,41 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>12</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>/news#mla-content-map-explained</t>
+          <t>/news#haematology-ukmla-revision</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2091,24 +2091,24 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>The Role of Mock Exams in UKMLA Preparation</t>
+          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>/news#mock-exams-ukmla-preparation</t>
+          <t>/news#how-long-does-gmc-registration-take</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2134,41 +2134,41 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>/news#nephrology-ukmla-revision</t>
+          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2177,41 +2177,41 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; The Medical Training Prioritisation Act 2026: What It Means for IMGs; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>/news#neurology-ukmla-revision</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2220,41 +2220,41 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
+          <t>How to Pass the UKMLA on Your First Attempt</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>/news#nice-guidelines-akt-revision</t>
+          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2263,41 +2263,41 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Resits: Rules, Limits, and How to Bounce Back; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
+          <t>/news#how-to-read-akt-stem</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2306,41 +2306,41 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
+          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>/news#ophthalmology-ent-ukmla-revision</t>
+          <t>/news#how-to-register-plab-1</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2349,41 +2349,41 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>/news#paediatrics-ukmla-revision</t>
+          <t>/news#infection-microbiology-ukmla-revision</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
+          <t>The Internship Requirement for GMC Registration, Explained</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>/news#palliative-care-ukmla-revision</t>
+          <t>/news#internship-requirement-for-gmc-registration</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2438,38 +2438,38 @@
         <v>2</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#is-indian-mbbs-valid-in-uk</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2478,37 +2478,41 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Official Resources; What Is the UKMLA?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
+          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>/news#pharmacology-prescribing-safety-ukmla</t>
+          <t>/news#is-ukmla-replacing-plab-explained</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2520,38 +2524,38 @@
         <v>2</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>Eligibility; Fees; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
+          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>/news#plab-2-preparation-guide</t>
+          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2563,38 +2567,38 @@
         <v>4</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How Long Does GMC Registration Take? A Realistic Timeline; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>/news#psychiatry-communication-cpsa-stations</t>
+          <t>/news#managing-ukmla-exam-anxiety</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2603,41 +2607,41 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Pass the UKMLA on Your First Attempt; UKMLA AKT Pass Mark and Pass Rate Explained; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Preparation; What Is an Angoff Standard Setting and Why Does It Matter?; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Radiology and Imaging Interpretation in the AKT</t>
+          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>/news#radiology-imaging-akt-ukmla</t>
+          <t>/news#mbbs-in-uk-for-indian-students</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2646,41 +2650,41 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Eligibility; Fees; MLA Content Map / Syllabus; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>/news#respiratory-medicine-ukmla-revision</t>
+          <t>/news#medical-training-initiative-scheme-closure-2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2689,41 +2693,41 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>GMC Regulation of Physician Associates: What Doctors Need to Know; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
+          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>/news#rheumatology-ukmla-revision</t>
+          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2732,41 +2736,41 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Eligibility; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>/news#safeguarding-ukmla-revision</t>
+          <t>/news#mental-health-ukmla-revision</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2775,37 +2779,41 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>/news#social-determinants-health-ukmla</t>
+          <t>/news#mla-content-map-explained</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2814,24 +2822,24 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2843,12 +2851,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>The Role of Mock Exams in UKMLA Preparation</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>/news#surgical-presentations-ukmla-revision</t>
+          <t>/news#mock-exams-ukmla-preparation</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2857,41 +2865,41 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>/news#three-months-ukmla-akt-countdown</t>
+          <t>/news#nephrology-ukmla-revision</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2900,41 +2908,41 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>24</v>
-      </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>/news#time-management-akt-ukmla</t>
+          <t>/news#neurology-ukmla-revision</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2943,41 +2951,41 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
+          <t>/news#nice-guidelines-akt-revision</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2986,41 +2994,41 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-medical-schools-ukmla-implementation</t>
+          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3029,41 +3037,41 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA?</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-guide-for-international-doctors</t>
+          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3075,21 +3083,21 @@
         <v>3</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Preparation; Registration Guide; Results and Scoring; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Requirements for International Doctors: The Complete Process; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3101,12 +3109,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-format-preparation</t>
+          <t>/news#ophthalmology-ent-ukmla-revision</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3115,41 +3123,41 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
+          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
+          <t>/news#paediatrics-ukmla-revision</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3158,41 +3166,41 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Results and Scoring; What Is an Angoff Standard Setting and Why Does It Matter?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-test-centres-guide</t>
+          <t>/news#palliative-care-ukmla-revision</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3201,41 +3209,41 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-cpsa-what-it-tests</t>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3244,41 +3252,37 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>CPSA Exam Pattern</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
+          <t>/news#pharmacology-prescribing-safety-ukmla</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3287,41 +3291,41 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+          <t>/news#plab-2-preparation-guide</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3330,41 +3334,41 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-explained</t>
+          <t>/news#psychiatry-communication-cpsa-stations</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3373,41 +3377,41 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+          <t>Radiology and Imaging Interpretation in the AKT</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-for-img-2026</t>
+          <t>/news#radiology-imaging-akt-ukmla</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3416,41 +3420,41 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-bangladeshi-doctors</t>
+          <t>/news#respiratory-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3459,41 +3463,41 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-egyptian-doctors</t>
+          <t>/news#rheumatology-ukmla-revision</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3502,41 +3506,41 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-filipino-doctors</t>
+          <t>/news#safeguarding-ukmla-revision</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3545,41 +3549,37 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-gulf-doctors</t>
+          <t>/news#social-determinants-health-ukmla</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3588,41 +3588,41 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
+          <t>/news#surgical-presentations-ukmla-revision</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3631,41 +3631,41 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-nigerian-doctors</t>
+          <t>/news#three-months-ukmla-akt-countdown</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3674,41 +3674,41 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>24</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-pakistani-doctors</t>
+          <t>/news#time-management-akt-ukmla</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3717,41 +3717,41 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-refugee-doctors</t>
+          <t>/news#types-of-gmc-registration-explained</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3763,38 +3763,38 @@
         <v>2</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+          <t>The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-south-african-doctors</t>
+          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3803,19 +3803,19 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Fees; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-sri-lankan-doctors</t>
+          <t>/news#uk-medical-schools-ukmla-implementation</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3846,41 +3846,41 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-graduate-entry-medical-students</t>
+          <t>/news#uk-visa-guide-for-international-doctors</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3889,24 +3889,24 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-key-dates-sitting-schedule</t>
+          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3932,41 +3932,41 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; OET vs IELTS for GMC Registration: Which Should You Take?</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Fees; Official Resources; Preparation; Results and Scoring; UKMLA vs PLAB; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Eligibility; Fees; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Key Dates</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-preparation-for-imgs</t>
+          <t>/news#ukmla-akt-format-preparation</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3975,41 +3975,41 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-question-bank-and-mock-tests</t>
+          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4018,41 +4018,41 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>How to Pass the UKMLA on Your First Attempt; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; Fees; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Appeals and Resits; Results and Scoring; What Is an Angoff Standard Setting and Why Does It Matter?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Results &amp; Scoring</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Results and Scoring</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-resits-rules-limits</t>
+          <t>/news#ukmla-akt-test-centres-guide</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4061,41 +4061,41 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Fees; Preparation; Results and Scoring; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-results-feedback-report</t>
+          <t>/news#ukmla-and-academic-foundation-programme</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4104,41 +4104,41 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Eligibility; Registration Guide; What Is the UKMLA?; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-revision-notes-strategy</t>
+          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4150,16 +4150,16 @@
         <v>4</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Pass the UKMLA on Your First Attempt; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Eligibility; Preparation; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-to-nhs-job-pathway</t>
+          <t>/news#ukmla-cpsa-what-it-tests</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4190,41 +4190,41 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+          <t>/news#ukmla-crash-course-for-doctors</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -4233,19 +4233,19 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained</t>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; UKMLA vs PLAB; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Preparation; MLA Content Map / Syllabus; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -4255,19 +4255,19 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-neet-pg</t>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -4276,41 +4276,41 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB: What Is the Difference?</t>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-plab-difference</t>
+          <t>/news#ukmla-exam-booking-process-gmc-online</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4319,41 +4319,41 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-usmle-comparison</t>
+          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4365,74 +4365,1192 @@
         <v>8</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Eligibility; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-explained</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-bangladeshi-doctors</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-egyptian-doctors</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-filipino-doctors</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-gulf-doctors</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-nigerian-doctors</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-pakistani-doctors</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-refugee-doctors</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Fees; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-south-african-doctors</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-sri-lankan-doctors</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-graduate-entry-medical-students</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-key-dates-sitting-schedule</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; Fees; Official Resources; Preparation; Results and Scoring; UKMLA vs PLAB; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-preparation-for-imgs</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; Fees; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-resits-rules-limits</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Results: How to Interpret Your Feedback Report; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Fees; Preparation; Results and Scoring; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-results-feedback-report</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-revision-notes-strategy</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Exam Preparation</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-syllabus-2026-changes</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus; UKMLA vs PLAB; How to Pass the UKMLA on Your First Attempt; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-to-nhs-job-pathway</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; UKMLA vs PLAB; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB: What Is the Difference?</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-plab-difference</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>/news#what-happens-if-you-fail-ukmla-foundation-year-impact</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; Results and Scoring; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
           <t>What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>/news#what-is-ukmla-complete-guide</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Blog Post</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="n">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E95" s="2" t="n">
+      <c r="E121" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>Understanding the Foundation Programme: What Awaits After the UKMLA; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
-      <c r="G95" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Core UKMLA Overview</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I95"/>
+  <autoFilter ref="A1:I121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4469,7 +5587,7 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>81</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3">
@@ -4489,7 +5607,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1158</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="5">
@@ -4499,7 +5617,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>14.3</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="6">
@@ -4558,7 +5676,7 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Respiratory Medicine for the UKMLA: What to Focus On (31 incoming)</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview (33 incoming)</t>
         </is>
       </c>
     </row>
@@ -4566,7 +5684,7 @@
       <c r="A14" s="5" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview (31 incoming)</t>
+          <t>Respiratory Medicine for the UKMLA: What to Focus On (31 incoming)</t>
         </is>
       </c>
     </row>
@@ -4582,7 +5700,7 @@
       <c r="A16" s="5" t="inlineStr"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT (26 incoming)</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting (28 incoming)</t>
         </is>
       </c>
     </row>
@@ -4590,7 +5708,7 @@
       <c r="A17" s="5" t="inlineStr"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More (26 incoming)</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT (26 incoming)</t>
         </is>
       </c>
     </row>
@@ -4598,7 +5716,7 @@
       <c r="A18" s="5" t="inlineStr"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting (26 incoming)</t>
+          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More (26 incoming)</t>
         </is>
       </c>
     </row>
@@ -4614,7 +5732,7 @@
       <c r="A20" s="5" t="inlineStr"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise (23 incoming)</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA (24 incoming)</t>
         </is>
       </c>
     </row>
@@ -4622,7 +5740,7 @@
       <c r="A21" s="5" t="inlineStr"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route (23 incoming)</t>
+          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise (23 incoming)</t>
         </is>
       </c>
     </row>

--- a/UKMLA_Internal_Linking_Map.xlsx
+++ b/UKMLA_Internal_Linking_Map.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +45,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +55,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -80,6 +85,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -448,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -526,14 +534,14 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -561,14 +569,14 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; OET vs IELTS for GMC Registration: Which Should You Take?; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Breaking Bad News in the CPSA: A Complete Guide; Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration for EU and Irish Doctors: What Changed After Brexit; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; The History of the UKMLA and PLAB Transition, Explained; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How to Write an NHS CV and Application That Gets Shortlisted; Indemnity Insurance for Doctors, Explained; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Locum vs Substantive NHS Posts: Which Is Right for You?; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The Multi-Specialty Recruitment Assessment (MSRA), Explained; OET vs IELTS for GMC Registration: Which Should You Take?; Relocating to the UK: A Practical Guide for IMG Doctors; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Transgender Health in the UKMLA: What the Content Map Covers; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; Urology in the UKMLA: High-Yield Topics for the AKT; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -596,14 +604,14 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Care of the Elderly and Frailty in the UKMLA: What to Revise; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Genetics and Genomics in the UKMLA: What You Need to Know; The GMC Annual Retention Fee, Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Medical Statistics and Evidence-Based Medicine in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; The Multi-Specialty Recruitment Assessment (MSRA), Explained; NICE Guidelines and the AKT: What You Actually Need to Know; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Substance Misuse and Addiction in the UKMLA: What to Revise; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -631,14 +639,14 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Breaking Bad News in the CPSA: A Complete Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The GMC Annual Retention Fee, Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; Medically Unexplained Symptoms in the UKMLA: What to Revise; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Write UKMLA Revision Notes That Actually Work; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -666,14 +674,14 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>The GMC Annual Retention Fee, Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Indemnity Insurance for Doctors, Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; The NHS Pension Scheme for Doctors, Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Understanding NHS Pay Scales and Banding for Doctors; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -736,14 +744,14 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Early Pregnancy Complications in the UKMLA: The Essential Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Genetics and Genomics in the UKMLA: What You Need to Know; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -771,14 +779,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; OET vs IELTS for GMC Registration: Which Should You Take?; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Breaking Bad News in the CPSA: A Complete Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Genetics and Genomics in the UKMLA: What You Need to Know; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Gynaecological Cancers in the UKMLA: Red Flags and Referral; The History of the UKMLA and PLAB Transition, Explained; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How to Write an NHS CV and Application That Gets Shortlisted; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; The Multi-Specialty Recruitment Assessment (MSRA), Explained; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; OET vs IELTS for GMC Registration: Which Should You Take?; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Public Health and Screening in the UKMLA: What You Need to Know; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -806,14 +814,14 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Internship Requirement for GMC Registration, Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs; OET vs IELTS for GMC Registration: Which Should You Take?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; How UK Medical Schools Implement the UKMLA: An Overview; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; The Certificate of Completion of Training (CCT), Explained; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; The History of the UKMLA and PLAB Transition, Explained; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Write an NHS CV and Application That Gets Shortlisted; Indemnity Insurance for Doctors, Explained; The Internship Requirement for GMC Registration, Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Locum vs Substantive NHS Posts: Which Is Right for You?; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The NHS e-Portfolio: A Practical Guide for Doctors; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; OET vs IELTS for GMC Registration: Which Should You Take?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Transgender Health in the UKMLA: What the Content Map Covers; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; How UK Medical Schools Implement the UKMLA: An Overview; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -841,14 +849,14 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The Role of Mock Exams in UKMLA Preparation; OET vs IELTS for GMC Registration: Which Should You Take?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The Role of Mock Exams in UKMLA Preparation; OET vs IELTS for GMC Registration: Which Should You Take?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -876,14 +884,14 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Breaking Bad News in the CPSA: A Complete Guide; Cardiology High-Yield Topics for the UKMLA AKT; Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Domestic Abuse and Adult Safeguarding in the UKMLA; Early Pregnancy Complications in the UKMLA: The Essential Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Genetics and Genomics in the UKMLA: What You Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Gynaecological Cancers in the UKMLA: Red Flags and Referral; The History of the UKMLA and PLAB Transition, Explained; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Immunology and Allergy in the UKMLA: High-Yield Revision; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Statistics and Evidence-Based Medicine in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Public Health and Screening in the UKMLA: What You Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Substance Misuse and Addiction in the UKMLA: What to Revise; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -911,14 +919,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MLA Content Map: The Blueprint Behind Every UKMLA Question; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; The History of the UKMLA and PLAB Transition, Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MLA Content Map: The Blueprint Behind Every UKMLA Question; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -946,14 +954,14 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Read an AKT Stem: Avoiding Common Traps; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; The History of the UKMLA and PLAB Transition, Explained; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Read an AKT Stem: Avoiding Common Traps; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -967,12 +975,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>/news#angoff-standard-setting-explained</t>
+          <t>/news#anaesthesia-and-perioperative-medicine-ukmla</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -981,41 +989,41 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>/news#blood-tests-data-interpretation-akt</t>
+          <t>/news#angoff-standard-setting-explained</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1024,41 +1032,41 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Medical Statistics and Evidence-Based Medicine in the UKMLA; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Results and Scoring</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>/news#cardiology-ukmla-akt-revision</t>
+          <t>/news#arcp-annual-review-of-competence-progression-explained</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1067,41 +1075,41 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>The Certificate of Completion of Training (CCT), Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained; The NHS e-Portfolio: A Practical Guide for Doctors</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>CPSA Exam Pattern; Registration Guide; The Certificate of Completion of Training (CCT), Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Locum vs Substantive NHS Posts: Which Is Right for You?; The Multi-Specialty Recruitment Assessment (MSRA), Explained; The NHS e-Portfolio: A Practical Guide for Doctors</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>/news#clinical-examination-cpsa-guide</t>
+          <t>/news#blood-tests-data-interpretation-akt</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1113,38 +1121,38 @@
         <v>15</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Medical Statistics and Evidence-Based Medicine in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Preparation; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know</t>
+          <t>Breaking Bad News in the CPSA: A Complete Guide</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>/news#dermatology-ukmla-revision</t>
+          <t>/news#breaking-bad-news-in-the-cpsa</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1152,42 +1160,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
-        <v>6</v>
+      <c r="D19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; Clinical Examination Stations in the CPSA: A Practical Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; The History of the UKMLA and PLAB Transition, Explained; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>/news#disability-access-ukmla-guide</t>
+          <t>/news#bringing-family-to-uk-dependent-visa-guide</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1196,41 +1204,41 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Relocating to the UK: A Practical Guide for IMG Doctors</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; UKMLA vs PLAB; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Eligibility; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>/news#ecg-interpretation-ukmla</t>
+          <t>/news#cardiology-ukmla-akt-revision</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1239,19 +1247,19 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1268,12 +1276,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Emergency Medicine and Acute Presentations in the UKMLA</t>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>/news#emergency-medicine-ukmla-revision</t>
+          <t>/news#care-of-the-elderly-and-frailty-ukmla</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1282,19 +1290,19 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Public Health and Screening in the UKMLA: What You Need to Know; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; MLA Content Map / Syllabus; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Public Health and Screening in the UKMLA: What You Need to Know; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1311,12 +1319,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
+          <t>The Certificate of Completion of Training (CCT), Explained</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>/news#endocrinology-diabetes-ukmla-revision</t>
+          <t>/news#certificate-of-completion-of-training-cct-explained</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1325,41 +1333,41 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Registration Guide; ARCP: The Annual Review of Competence Progression, Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The GMC Revalidation Process, Explained for New Doctors; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Multi-Specialty Recruitment Assessment (MSRA), Explained; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
+          <t>Chronic Pain Management in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>/news#english-language-requirement-for-ukmla-india</t>
+          <t>/news#chronic-pain-management-ukmla</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1368,41 +1376,41 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Immunology and Allergy in the UKMLA: High-Yield Revision</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>MLA Content Map / Syllabus; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-programme-2026-recruitment-changes</t>
+          <t>/news#clinical-examination-cpsa-guide</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1411,41 +1419,41 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Regulation of Physician Associates: What Doctors Need to Know; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Key Dates; Preparation; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Preparation; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-programme-after-ukmla</t>
+          <t>/news#consent-and-mental-capacity-ukmla</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1454,37 +1462,41 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Domestic Abuse and Adult Safeguarding in the UKMLA; Medical Statistics and Evidence-Based Medicine in the UKMLA; Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>CPSA Exam Pattern; MLA Content Map / Syllabus; Domestic Abuse and Adult Safeguarding in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide; Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
+          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
+          <t>/news#contraception-counselling-ukmla</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1493,41 +1505,41 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
+          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide; Menopause Management in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>CPSA Exam Pattern; MLA Content Map / Syllabus; Early Pregnancy Complications in the UKMLA: The Essential Guide; Menopause Management in the UKMLA: What You Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>/news#gastroenterology-ukmla-akt-revision</t>
+          <t>/news#critical-care-and-intensive-care-basics-ukmla</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1535,20 +1547,20 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>8</v>
-      </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Substance Misuse and Addiction in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>MLA Content Map / Syllabus; Chronic Pain Management in the UKMLA: What to Revise; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Substance Misuse and Addiction in the UKMLA: What to Revise; Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1565,12 +1577,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-english-language-exemption-for-imgs</t>
+          <t>/news#dermatology-ukmla-revision</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1579,41 +1591,41 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
+          <t>/news#disability-access-ukmla-guide</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1622,41 +1634,41 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; UKMLA vs PLAB; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Appeals and Resits</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
+          <t>Domestic Abuse and Adult Safeguarding in the UKMLA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
+          <t>/news#domestic-abuse-and-safeguarding-adults-ukmla</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1665,41 +1677,41 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Medically Unexplained Symptoms in the UKMLA: What to Revise; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>MLA Content Map / Syllabus; Consent and Mental Capacity in the UKMLA: The Complete Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Medically Unexplained Symptoms in the UKMLA: What to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
+          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-recognised-primary-medical-qualifications</t>
+          <t>/news#early-pregnancy-complications-ukmla</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1708,41 +1720,41 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>The Internship Requirement for GMC Registration, Explained; OET vs IELTS for GMC Registration: Which Should You Take?</t>
+          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Menopause Management in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>AKT Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; Contraception Counselling in the UKMLA: A Complete Revision Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
+          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-and-epic-verification-india</t>
+          <t>/news#ecg-interpretation-ukmla</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1751,41 +1763,41 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
+          <t>Emergency Medicine and Acute Presentations in the UKMLA</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-refund-policy</t>
+          <t>/news#emergency-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1794,41 +1806,41 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How Long Does GMC Registration Take? A Realistic Timeline; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Early Pregnancy Complications in the UKMLA: The Essential Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Immunology and Allergy in the UKMLA: High-Yield Revision; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Fees; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>AKT Exam Pattern; Preparation; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
+          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-requirements-for-international-doctors</t>
+          <t>/news#endocrinology-diabetes-ukmla-revision</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1837,41 +1849,41 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Menopause Management in the UKMLA: What You Need to Know; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
+          <t>/news#english-language-requirement-for-ukmla-india</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1880,41 +1892,41 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; Good Medical Practice and the UKMLA: What the GMC Expects; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>Eligibility; Official Resources; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>The GMC Revalidation Process, Explained for New Doctors</t>
+          <t>Working Hours and Rest Rules for Doctors: The EWTD Explained</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-revalidation-process-explained</t>
+          <t>/news#ewtd-working-hours-and-rest-rules-for-doctors</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1926,21 +1938,21 @@
         <v>3</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Locum vs Substantive NHS Posts: Which Is Right for You?; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Official Resources; Registration Guide; ARCP: The Annual Review of Competence Progression, Explained; Understanding the Foundation Programme: What Awaits After the UKMLA; Locum vs Substantive NHS Posts: Which Is Right for You?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -1952,12 +1964,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
+          <t>/news#foundation-programme-2026-recruitment-changes</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1966,41 +1978,41 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; OET vs IELTS for GMC Registration: Which Should You Take?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Regulation of Physician Associates: What Doctors Need to Know; The Multi-Specialty Recruitment Assessment (MSRA), Explained; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Preparation; Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Key Dates; Preparation; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>/news#good-medical-practice-ukmla</t>
+          <t>/news#foundation-programme-after-ukmla</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2009,24 +2021,24 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Indemnity Insurance for Doctors, Explained; The Internship Requirement for GMC Registration, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; Relocating to the UK: A Practical Guide for IMG Doctors; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2034,12 +2046,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>/news#group-study-vs-solo-ukmla</t>
+          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2048,41 +2060,41 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>The Certificate of Completion of Training (CCT), Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
+          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>/news#haematology-ukmla-revision</t>
+          <t>/news#gastroenterology-ukmla-akt-revision</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2091,19 +2103,19 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2120,12 +2132,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
+          <t>Genetics and Genomics in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>/news#how-long-does-gmc-registration-take</t>
+          <t>/news#genetics-and-genomics-in-the-ukmla</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2137,38 +2149,38 @@
         <v>2</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
+          <t>Sepsis Recognition and Management in the UKMLA: The Essential Guide; Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
+          <t>AKT Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
+          <t>The GMC Annual Retention Fee, Explained</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
+          <t>/news#gmc-annual-retention-fee-explained</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2177,41 +2189,41 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; The Medical Training Prioritisation Act 2026: What It Means for IMGs; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>The NHS e-Portfolio: A Practical Guide for Doctors; The NHS Pension Scheme for Doctors, Explained; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Fees; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
+          <t>/news#gmc-english-language-exemption-for-imgs</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2220,24 +2232,24 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Eligibility; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2249,12 +2261,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>How to Pass the UKMLA on Your First Attempt</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
+          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2266,38 +2278,38 @@
         <v>4</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Indemnity Insurance for Doctors, Explained</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Resits: Rules, Limits, and How to Bounce Back; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-read-akt-stem</t>
+          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2306,41 +2318,41 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-register-plab-1</t>
+          <t>/news#gmc-recognised-primary-medical-qualifications</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2349,19 +2361,19 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; The Internship Requirement for GMC Registration, Explained; OET vs IELTS for GMC Registration: Which Should You Take?; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Eligibility; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2371,19 +2383,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>/news#infection-microbiology-ukmla-revision</t>
+          <t>/news#gmc-registration-and-epic-verification-india</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2392,41 +2404,41 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>The Internship Requirement for GMC Registration, Explained</t>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>/news#internship-requirement-for-gmc-registration</t>
+          <t>/news#gmc-registration-for-eu-and-irish-doctors</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2438,21 +2450,21 @@
         <v>2</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline</t>
+          <t>UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>Eligibility; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2464,12 +2476,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>/news#is-indian-mbbs-valid-in-uk</t>
+          <t>/news#gmc-registration-refund-policy</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2478,41 +2490,41 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The GMC Annual Retention Fee, Explained; How Long Does GMC Registration Take? A Realistic Timeline; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; What Is the UKMLA?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Fees; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>/news#is-ukmla-replacing-plab-explained</t>
+          <t>/news#gmc-registration-requirements-for-international-doctors</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2521,41 +2533,41 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; Relocating to the UK: A Practical Guide for IMG Doctors; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Eligibility; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
+          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
+          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2564,24 +2576,24 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How Long Does GMC Registration Take? A Realistic Timeline; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; AKT Exam Pattern; Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; Good Medical Practice and the UKMLA: What the GMC Expects; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2593,12 +2605,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
+          <t>The GMC Revalidation Process, Explained for New Doctors</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>/news#managing-ukmla-exam-anxiety</t>
+          <t>/news#gmc-revalidation-process-explained</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2607,41 +2619,41 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Pass the UKMLA on Your First Attempt; UKMLA AKT Pass Mark and Pass Rate Explained; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>The Certificate of Completion of Training (CCT), Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; The NHS e-Portfolio: A Practical Guide for Doctors; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Preparation; What Is an Angoff Standard Setting and Why Does It Matter?; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
+          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>/news#mbbs-in-uk-for-indian-students</t>
+          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2650,41 +2662,41 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; OET vs IELTS for GMC Registration: Which Should You Take?; Relocating to the UK: A Practical Guide for IMG Doctors; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; MLA Content Map / Syllabus; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Preparation; Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>/news#medical-training-initiative-scheme-closure-2026</t>
+          <t>/news#good-medical-practice-ukmla</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2693,41 +2705,37 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>GMC Regulation of Physician Associates: What Doctors Need to Know; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Domestic Abuse and Adult Safeguarding in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; Indemnity Insurance for Doctors, Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
+          <t>/news#group-study-vs-solo-ukmla</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2736,41 +2744,41 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
+          <t>Gynaecological Cancers in the UKMLA: Red Flags and Referral</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>/news#mental-health-ukmla-revision</t>
+          <t>/news#gynaecological-cancers-ukmla</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2779,19 +2787,19 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide; Public Health and Screening in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Medical Statistics and Evidence-Based Medicine in the UKMLA; Menopause Management in the UKMLA: What You Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2808,12 +2816,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>/news#mla-content-map-explained</t>
+          <t>/news#haematology-ukmla-revision</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2822,24 +2830,24 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Genetics and Genomics in the UKMLA: What You Need to Know; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -2851,12 +2859,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>The Role of Mock Exams in UKMLA Preparation</t>
+          <t>The History of the UKMLA and PLAB Transition, Explained</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>/news#mock-exams-ukmla-preparation</t>
+          <t>/news#history-of-ukmla-plab-transition-explained</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2864,42 +2872,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n">
-        <v>15</v>
+      <c r="D59" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Breaking Bad News in the CPSA: A Complete Guide</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Eligibility; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA Exam Day: What to Expect at the AKT and CPSA; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
+          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>/news#nephrology-ukmla-revision</t>
+          <t>/news#how-long-does-gmc-registration-take</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2908,41 +2916,41 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>/news#neurology-ukmla-revision</t>
+          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2951,41 +2959,41 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; The Medical Training Prioritisation Act 2026: What It Means for IMGs; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>/news#nice-guidelines-akt-revision</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -2994,41 +3002,41 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
+          <t>How to Pass the UKMLA on Your First Attempt</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
+          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3037,41 +3045,41 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Resits: Rules, Limits, and How to Bounce Back; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
+          <t>/news#how-to-read-akt-stem</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3080,41 +3088,41 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Preparation; Registration Guide; Results and Scoring; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Requirements for International Doctors: The Complete Process; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
+          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>/news#ophthalmology-ent-ukmla-revision</t>
+          <t>/news#how-to-register-plab-1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3123,41 +3131,41 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>How to Write an NHS CV and Application That Gets Shortlisted</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>/news#paediatrics-ukmla-revision</t>
+          <t>/news#how-to-write-an-nhs-cv-and-application</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3165,42 +3173,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n">
-        <v>28</v>
+      <c r="D66" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Eligibility; Preparation; Registration Guide; Locum vs Substantive NHS Posts: Which Is Right for You?; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Relocating to the UK: A Practical Guide for IMG Doctors; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
+          <t>Immunology and Allergy in the UKMLA: High-Yield Revision</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>/news#palliative-care-ukmla-revision</t>
+          <t>/news#immunology-and-allergy-ukmla</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3208,20 +3216,20 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n">
-        <v>2</v>
+      <c r="D67" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>MLA Content Map / Syllabus; Chronic Pain Management in the UKMLA: What to Revise; Emergency Medicine and Acute Presentations in the UKMLA; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3238,12 +3246,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>Indemnity Insurance for Doctors, Explained</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#indemnity-insurance-for-doctors-explained</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3251,38 +3259,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D68" s="2" t="n">
-        <v>28</v>
+      <c r="D68" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>The NHS Pension Scheme for Doctors, Explained</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Fees; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; The NHS Pension Scheme for Doctors, Explained; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
+          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>/news#pharmacology-prescribing-safety-ukmla</t>
+          <t>/news#infection-microbiology-ukmla-revision</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3291,19 +3303,19 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3320,12 +3332,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
+          <t>The Internship Requirement for GMC Registration, Explained</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>/news#plab-2-preparation-guide</t>
+          <t>/news#internship-requirement-for-gmc-registration</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3334,41 +3346,41 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>/news#psychiatry-communication-cpsa-stations</t>
+          <t>/news#is-indian-mbbs-valid-in-uk</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3377,41 +3389,41 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Official Resources; What Is the UKMLA?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Radiology and Imaging Interpretation in the AKT</t>
+          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>/news#radiology-imaging-akt-ukmla</t>
+          <t>/news#is-ukmla-replacing-plab-explained</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3420,41 +3432,41 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>The History of the UKMLA and PLAB Transition, Explained; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Eligibility; Fees; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>/news#respiratory-medicine-ukmla-revision</t>
+          <t>/news#joining-a-royal-college-mrcp-mrcs-mrcgp-overview</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3463,41 +3475,41 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; The Certificate of Completion of Training (CCT), Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Registration Guide; Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; The Certificate of Completion of Training (CCT), Explained; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
+          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>/news#rheumatology-ukmla-revision</t>
+          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3506,41 +3518,41 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>The Certificate of Completion of Training (CCT), Explained; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How Long Does GMC Registration Take? A Realistic Timeline; Locum vs Substantive NHS Posts: Which Is Right for You?; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>Locum vs Substantive NHS Posts: Which Is Right for You?</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>/news#safeguarding-ukmla-revision</t>
+          <t>/news#locum-vs-substantive-nhs-posts-explained</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3549,37 +3561,41 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>11</v>
-      </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; How to Write an NHS CV and Application That Gets Shortlisted; The NHS e-Portfolio: A Practical Guide for Doctors</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>Eligibility; Registration Guide; Working Hours and Rest Rules for Doctors: The EWTD Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The NHS e-Portfolio: A Practical Guide for Doctors; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>/news#social-determinants-health-ukmla</t>
+          <t>/news#managing-ukmla-exam-anxiety</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3588,41 +3604,41 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Breaking Bad News in the CPSA: A Complete Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Working Hours and Rest Rules for Doctors: The EWTD Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Pass the UKMLA on Your First Attempt; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Special Circumstances: Accommodations Beyond Disability Access; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Preparation; What Is an Angoff Standard Setting and Why Does It Matter?; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>/news#surgical-presentations-ukmla-revision</t>
+          <t>/news#mbbs-in-uk-for-indian-students</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3631,41 +3647,41 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Eligibility; Fees; MLA Content Map / Syllabus; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Medical Statistics and Evidence-Based Medicine in the UKMLA</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>/news#three-months-ukmla-akt-countdown</t>
+          <t>/news#medical-statistics-and-evidence-based-medicine-ukmla</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3674,41 +3690,41 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Gynaecological Cancers in the UKMLA: Red Flags and Referral; Public Health and Screening in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>AKT Exam Pattern; MLA Content Map / Syllabus; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Public Health and Screening in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>/news#time-management-akt-ukmla</t>
+          <t>/news#medical-training-initiative-scheme-closure-2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3717,41 +3733,41 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>GMC Regulation of Physician Associates: What Doctors Need to Know; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Eligibility; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>/news#types-of-gmc-registration-explained</t>
+          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3763,38 +3779,38 @@
         <v>2</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>Eligibility; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
+          <t>Medically Unexplained Symptoms in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
+          <t>/news#medically-unexplained-symptoms-ukmla</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3803,41 +3819,41 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Domestic Abuse and Adult Safeguarding in the UKMLA; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Domestic Abuse and Adult Safeguarding in the UKMLA; Mental Health Presentations in the UKMLA: What to Revise; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Menopause Management in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-medical-schools-ukmla-implementation</t>
+          <t>/news#menopause-management-ukmla</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3846,41 +3862,41 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide; Gynaecological Cancers in the UKMLA: Red Flags and Referral</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Contraception Counselling in the UKMLA: A Complete Revision Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA?</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-guide-for-international-doctors</t>
+          <t>/news#mental-health-ukmla-revision</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3889,41 +3905,41 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Medically Unexplained Symptoms in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Substance Misuse and Addiction in the UKMLA: What to Revise; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
+          <t>/news#mla-content-map-explained</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3932,41 +3948,41 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; OET vs IELTS for GMC Registration: Which Should You Take?</t>
+          <t>Genetics and Genomics in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>The Role of Mock Exams in UKMLA Preparation</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-format-preparation</t>
+          <t>/news#mock-exams-ukmla-preparation</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3975,41 +3991,41 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Breaking Bad News in the CPSA: A Complete Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
+          <t>The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
+          <t>/news#multi-specialty-recruitment-assessment-msra-explained</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4018,41 +4034,41 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>How to Pass the UKMLA on Your First Attempt; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; The Certificate of Completion of Training (CCT), Explained</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Results and Scoring; What Is an Angoff Standard Setting and Why Does It Matter?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>Eligibility; AKT Exam Pattern; Preparation; ARCP: The Annual Review of Competence Progression, Explained; The Certificate of Completion of Training (CCT), Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Good Medical Practice and the UKMLA: What the GMC Expects; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-test-centres-guide</t>
+          <t>/news#nephrology-ukmla-revision</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4061,41 +4077,41 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Genetics and Genomics in the UKMLA: What You Need to Know; NICE Guidelines and the AKT: What You Actually Need to Know; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
+          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-and-academic-foundation-programme</t>
+          <t>/news#neurology-ukmla-revision</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4104,41 +4120,41 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; What Is the UKMLA?; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
+          <t>The NHS e-Portfolio: A Practical Guide for Doctors</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
+          <t>/news#nhs-eportfolio-guide-for-doctors</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4147,41 +4163,41 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Pass the UKMLA on Your First Attempt; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Locum vs Substantive NHS Posts: Which Is Right for You?</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Preparation; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Registration Guide; ARCP: The Annual Review of Competence Progression, Explained; The GMC Annual Retention Fee, Explained; The GMC Revalidation Process, Explained for New Doctors; Locum vs Substantive NHS Posts: Which Is Right for You?; How to Write UKMLA Revision Notes That Actually Work; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-cpsa-what-it-tests</t>
+          <t>/news#nhs-job-interview-preparation-guide</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4190,41 +4206,41 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>How to Write an NHS CV and Application That Gets Shortlisted; Relocating to the UK: A Practical Guide for IMG Doctors</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Registration Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Write an NHS CV and Application That Gets Shortlisted; Relocating to the UK: A Practical Guide for IMG Doctors; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+          <t>The NHS Pension Scheme for Doctors, Explained</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-crash-course-for-doctors</t>
+          <t>/news#nhs-pension-scheme-for-doctors-explained</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -4233,41 +4249,41 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Indemnity Insurance for Doctors, Explained; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Fees; The GMC Annual Retention Fee, Explained; Indemnity Insurance for Doctors, Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
+          <t>/news#nice-guidelines-akt-revision</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -4276,41 +4292,41 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exam-booking-process-gmc-online</t>
+          <t>/news#nutrition-and-metabolic-disorders-ukmla</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4318,42 +4334,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D93" s="2" t="n">
-        <v>2</v>
+      <c r="D93" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
+          <t>Immunology and Allergy in the UKMLA: High-Yield Revision</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Care of the Elderly and Frailty in the UKMLA: What to Revise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Immunology and Allergy in the UKMLA: High-Yield Revision; Substance Misuse and Addiction in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4362,41 +4378,41 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Contraception Counselling in the UKMLA: A Complete Revision Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Menopause Management in the UKMLA: What You Need to Know; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-explained</t>
+          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -4408,16 +4424,16 @@
         <v>5</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Eligibility; Preparation; Registration Guide; Results and Scoring; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Requirements for International Doctors: The Complete Process; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -4427,19 +4443,19 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-for-img-2026</t>
+          <t>/news#ophthalmology-ent-ukmla-revision</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -4448,41 +4464,41 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-bangladeshi-doctors</t>
+          <t>/news#paediatrics-ukmla-revision</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4491,41 +4507,41 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-egyptian-doctors</t>
+          <t>/news#palliative-care-ukmla-revision</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -4534,41 +4550,41 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-filipino-doctors</t>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4577,41 +4593,37 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Menopause Management in the UKMLA: What You Need to Know; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Substance Misuse and Addiction in the UKMLA: What to Revise; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; Urology in the UKMLA: High-Yield Topics for the AKT; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>Eligibility</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-gulf-doctors</t>
+          <t>/news#pharmacology-prescribing-safety-ukmla</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -4620,41 +4632,41 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Immunology and Allergy in the UKMLA: High-Yield Revision; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Public Health and Screening in the UKMLA: What You Need to Know; Substance Misuse and Addiction in the UKMLA: What to Revise; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
+          <t>/news#plab-2-preparation-guide</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4663,41 +4675,41 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-nigerian-doctors</t>
+          <t>/news#prescribing-in-renal-and-hepatic-impairment-ukmla</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -4706,41 +4718,41 @@
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Medically Unexplained Symptoms in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>MLA Content Map / Syllabus; Domestic Abuse and Adult Safeguarding in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-pakistani-doctors</t>
+          <t>/news#psychiatry-communication-cpsa-stations</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4749,41 +4761,41 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Domestic Abuse and Adult Safeguarding in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>Public Health and Screening in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-refugee-doctors</t>
+          <t>/news#public-health-and-screening-ukmla</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4792,41 +4804,41 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Medical Statistics and Evidence-Based Medicine in the UKMLA</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>Preparation; MLA Content Map / Syllabus; Care of the Elderly and Frailty in the UKMLA: What to Revise; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Medical Statistics and Evidence-Based Medicine in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Radiology and Imaging Interpretation in the AKT</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-south-african-doctors</t>
+          <t>/news#radiology-imaging-akt-ukmla</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4835,41 +4847,41 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Relocating to the UK: A Practical Guide for IMG Doctors</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-sri-lankan-doctors</t>
+          <t>/news#relocating-to-the-uk-a-practical-guide-for-img-doctors</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4878,19 +4890,19 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; How to Write an NHS CV and Application That Gets Shortlisted; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Eligibility; Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -4907,12 +4919,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-graduate-entry-medical-students</t>
+          <t>/news#respiratory-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4921,41 +4933,41 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-key-dates-sitting-schedule</t>
+          <t>/news#returning-to-practise-in-gulf-countries-dataflow-guide</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4964,41 +4976,41 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Fees; Official Resources; Preparation; Results and Scoring; UKMLA vs PLAB; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Eligibility; Registration Guide; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Key Dates</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-preparation-for-imgs</t>
+          <t>/news#rheumatology-ukmla-revision</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5007,41 +5019,41 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Immunology and Allergy in the UKMLA: High-Yield Revision; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-question-bank-and-mock-tests</t>
+          <t>/news#safeguarding-ukmla-revision</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5050,41 +5062,37 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Domestic Abuse and Adult Safeguarding in the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; Fees; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>Preparation</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-resits-rules-limits</t>
+          <t>/news#scotland-wales-northern-ireland-registration-differences</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5092,20 +5100,20 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D111" s="2" t="n">
-        <v>7</v>
+      <c r="D111" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Results: How to Interpret Your Feedback Report; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Fees; Preparation; Results and Scoring; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Eligibility; Official Resources; Registration Guide; The GMC Annual Retention Fee, Explained; GMC Registration Requirements for International Doctors: The Complete Process; The GMC Revalidation Process, Explained for New Doctors; Relocating to the UK: A Practical Guide for IMG Doctors; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -5115,19 +5123,19 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-results-feedback-report</t>
+          <t>/news#sepsis-recognition-and-management-ukmla</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5136,41 +5144,41 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Genetics and Genomics in the UKMLA: What You Need to Know; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Genetics and Genomics in the UKMLA: What You Need to Know; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-revision-notes-strategy</t>
+          <t>/news#social-determinants-health-ukmla</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5179,41 +5187,41 @@
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Public Health and Screening in the UKMLA: What You Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Substance Misuse and Addiction in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-syllabus-2026-changes</t>
+          <t>/news#substance-misuse-and-addiction-ukmla</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5222,24 +5230,24 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus; UKMLA vs PLAB; How to Pass the UKMLA on Your First Attempt; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+          <t>AKT Exam Pattern; MLA Content Map / Syllabus; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Mental Health Presentations in the UKMLA: What to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5251,12 +5259,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-to-nhs-job-pathway</t>
+          <t>/news#surgical-presentations-ukmla-revision</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -5265,41 +5273,41 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+          <t>/news#three-months-ukmla-akt-countdown</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5308,41 +5316,41 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained</t>
+          <t>How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; UKMLA vs PLAB; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-neet-pg</t>
+          <t>/news#time-management-akt-ukmla</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -5351,41 +5359,41 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-plab-difference</t>
+          <t>/news#toxicology-and-poisoning-ukmla</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5394,41 +5402,41 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Substance Misuse and Addiction in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-vs-usmle-comparison</t>
+          <t>/news#transgender-health-in-the-ukmla</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -5437,41 +5445,41 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Genetics and Genomics in the UKMLA: What You Need to Know; Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; MLA Content Map / Syllabus; Consent and Mental Capacity in the UKMLA: The Complete Guide; Genetics and Genomics in the UKMLA: What You Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>/news#what-happens-if-you-fail-ukmla-foundation-year-impact</t>
+          <t>/news#trauma-and-orthopaedics-ukmla</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5480,77 +5488,2223 @@
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; Results and Scoring; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>AKT Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>/news#types-of-gmc-registration-explained</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>The Certificate of Completion of Training (CCT), Explained; The GMC Annual Retention Fee, Explained; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The NHS Pension Scheme for Doctors, Explained; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Fees; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>/news#uk-medical-schools-ukmla-implementation</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>What Is the UKMLA?</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>/news#uk-visa-guide-for-international-doctors</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Indemnity Insurance for Doctors, Explained; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Locum vs Substantive NHS Posts: Which Is Right for You?; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; OET vs IELTS for GMC Registration: Which Should You Take?</t>
+        </is>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Fees; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-akt-format-preparation</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Exam Format</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>How to Pass the UKMLA on Your First Attempt; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Results and Scoring; What Is an Angoff Standard Setting and Why Does It Matter?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-akt-test-centres-guide</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-and-academic-foundation-programme</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; What Is the UKMLA?; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Pass the UKMLA on Your First Attempt; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Preparation; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Exam Preparation</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-cpsa-what-it-tests</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Breaking Bad News in the CPSA: A Complete Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Exam Format</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>CPSA Exam Pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-crash-course-for-doctors</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>Preparation; MLA Content Map / Syllabus; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exam-booking-process-gmc-online</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Day: What to Expect at the AKT and CPSA</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exam-day-what-to-expect</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>The History of the UKMLA and PLAB Transition, Explained; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-explained</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-fees-for-img-2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>The GMC Annual Retention Fee, Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-bangladeshi-doctors</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-chinese-doctors</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-egyptian-doctors</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-filipino-doctors</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-gulf-doctors</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-jamaican-and-trinidadian-doctors</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration for EU and Irish Doctors: What Changed After Brexit; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-jordanian-and-iraqi-doctors</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Fees; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-kenyan-and-east-african-doctors</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration for EU and Irish Doctors: What Changed After Brexit; MLA Content Map: The Blueprint Behind Every UKMLA Question; Psychiatry Communication Stations: Handling Difficult Conversations; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-nigerian-doctors</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-pakistani-doctors</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-refugee-doctors</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Fees; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-south-african-doctors</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-sri-lankan-doctors</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-for-vietnamese-and-indonesian-doctors</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA for Graduate-Entry Medical Students: What Is Different?</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-graduate-entry-medical-students</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Key Dates and Sitting Schedule: What to Know</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-key-dates-sitting-schedule</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; Fees; Official Resources; Preparation; Results and Scoring; UKMLA vs PLAB; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>Key Dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-preparation-for-imgs</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>Breaking Bad News in the CPSA: A Complete Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Write an NHS CV and Application That Gets Shortlisted; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The Multi-Specialty Recruitment Assessment (MSRA), Explained; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Relocating to the UK: A Practical Guide for IMG Doctors; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-question-bank-and-mock-tests</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Indemnity Insurance for Doctors, Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; Fees; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-resits-rules-limits</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>Breaking Bad News in the CPSA: A Complete Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Results: How to Interpret Your Feedback Report; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Fees; Preparation; Results and Scoring; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-results-feedback-report</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>Results and Scoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>How to Write UKMLA Revision Notes That Actually Work</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-revision-notes-strategy</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The NHS e-Portfolio: A Practical Guide for Doctors; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Exam Preparation</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Preparation</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-special-circumstances-and-accommodations</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>Breaking Bad News in the CPSA: A Complete Guide</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; CPSA Exam Pattern; Registration Guide; Breaking Bad News in the CPSA: A Complete Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Exam Day: What to Expect at the AKT and CPSA</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-syllabus-2026-changes</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>Genetics and Genomics in the UKMLA: What You Need to Know; The History of the UKMLA and PLAB Transition, Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Menopause Management in the UKMLA: What You Need to Know; Public Health and Screening in the UKMLA: What You Need to Know; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus; UKMLA vs PLAB; How to Pass the UKMLA on Your First Attempt; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-to-nhs-job-pathway</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Write an NHS CV and Application That Gets Shortlisted; Indemnity Insurance for Doctors, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Locum vs Substantive NHS Posts: Which Is Right for You?; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The NHS e-Portfolio: A Practical Guide for Doctors; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; The NHS Pension Scheme for Doctors, Explained; Relocating to the UK: A Practical Guide for IMG Doctors; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; Understanding NHS Pay Scales and Banding for Doctors</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; Registration Guide; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-amc-and-mccqe-comparison</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; UKMLA vs PLAB; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-neet-pg</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB: What Is the Difference?</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-plab-difference</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G166" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Core UKMLA Overview</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>/news#ukmla-vs-usmle-comparison</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+        </is>
+      </c>
+      <c r="G167" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Fees; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>UKMLA vs PLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Understanding NHS Pay Scales and Banding for Doctors</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>/news#understanding-nhs-pay-scales-and-banding-for-doctors</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>Working Hours and Rest Rules for Doctors: The EWTD Explained; The NHS Pension Scheme for Doctors, Explained; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>Fees; Working Hours and Rest Rules for Doctors: The EWTD Explained; The NHS Pension Scheme for Doctors, Explained; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Urology in the UKMLA: High-Yield Topics for the AKT</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>/news#urology-ukmla-revision</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management</t>
+        </is>
+      </c>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>Eligibility; AKT Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; Care of the Elderly and Frailty in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>/news#what-happens-if-you-fail-ukmla-foundation-year-impact</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; Results and Scoring; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Results &amp; Scoring</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Appeals and Resits</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
           <t>What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>/news#what-is-ukmla-complete-guide</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Blog Post</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E121" s="2" t="n">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Blog Post</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E171" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA AKT: Format, Question Types, and How to Prepare</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA; The History of the UKMLA and PLAB Transition, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
         <is>
           <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>Core UKMLA Overview</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I121"/>
+  <autoFilter ref="A1:I171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5569,178 +7723,178 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Total blog posts</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
-        <v>107</v>
+      <c r="B2" s="6" t="n">
+        <v>157</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Total pillar/site pages tracked</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Total outgoing links (from posts)</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>1397</v>
+      <c r="B4" s="6" t="n">
+        <v>1810</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Avg outgoing links per post</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>13.1</v>
+      <c r="B5" s="6" t="n">
+        <v>11.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Posts with 0 incoming links</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Posts with 1 incoming link</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>0</v>
+      <c r="B7" s="6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Posts needing more internal links (0 incoming):</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Most heavily interlinked posts (by incoming links):</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
+      <c r="B11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know (33 incoming)</t>
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting (38 incoming)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know (37 incoming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>How UK Medical Schools Implement the UKMLA: An Overview (33 incoming)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Respiratory Medicine for the UKMLA: What to Focus On (31 incoming)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide (28 incoming)</t>
-        </is>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting (28 incoming)</t>
+      <c r="A16" s="6" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA (30 incoming)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide (29 incoming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide (27 incoming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More (27 incoming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Cardiology High-Yield Topics for the UKMLA AKT (26 incoming)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More (26 incoming)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide (25 incoming)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA (24 incoming)</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise (23 incoming)</t>
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>UKMLA Preparation for IMG Candidates: A Tailored Guide (25 incoming)</t>
         </is>
       </c>
     </row>

--- a/UKMLA_Internal_Linking_Map.xlsx
+++ b/UKMLA_Internal_Linking_Map.xlsx
@@ -639,14 +639,14 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ARCP: The Annual Review of Competence Progression, Explained; Breaking Bad News in the CPSA: A Complete Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The GMC Annual Retention Fee, Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Good Medical Practice and the UKMLA: What the GMC Expects; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; Medically Unexplained Symptoms in the UKMLA: What to Revise; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Write UKMLA Revision Notes That Actually Work; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Breaking Bad News in the CPSA: A Complete Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The GMC Annual Retention Fee, Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; Medically Unexplained Symptoms in the UKMLA: What to Revise; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Write UKMLA Revision Notes That Actually Work; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -1634,14 +1634,14 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>17</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2536,7 +2536,7 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Eligibility; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2959,14 +2959,14 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>18</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; The Medical Training Prioritisation Act 2026: What It Means for IMGs; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -5663,7 +5663,7 @@
         <v>8</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
         <v>3</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1810</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="5">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="6">

--- a/UKMLA_Internal_Linking_Map.xlsx
+++ b/UKMLA_Internal_Linking_Map.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internal Linking Map'!$A$1:$I$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I171"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -569,14 +569,14 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Breaking Bad News in the CPSA: A Complete Guide; Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration for EU and Irish Doctors: What Changed After Brexit; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; The History of the UKMLA and PLAB Transition, Explained; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How to Write an NHS CV and Application That Gets Shortlisted; Indemnity Insurance for Doctors, Explained; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Locum vs Substantive NHS Posts: Which Is Right for You?; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The Multi-Specialty Recruitment Assessment (MSRA), Explained; OET vs IELTS for GMC Registration: Which Should You Take?; Relocating to the UK: A Practical Guide for IMG Doctors; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Transgender Health in the UKMLA: What the Content Map Covers; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; Urology in the UKMLA: High-Yield Topics for the AKT; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; Breaking Bad News in the CPSA: A Complete Guide; Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC EPIC/MyIntealth Verification Process Explained; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration for EU and Irish Doctors: What Changed After Brexit; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; The History of the UKMLA and PLAB Transition, Explained; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How to Write an NHS CV and Application That Gets Shortlisted; Indemnity Insurance for Doctors, Explained; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Locum vs Substantive NHS Posts: Which Is Right for You?; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The Multi-Specialty Recruitment Assessment (MSRA), Explained; OET vs IELTS for GMC Registration: Which Should You Take?; Relocating to the UK: A Practical Guide for IMG Doctors; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Transgender Health in the UKMLA: What the Content Map Covers; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA After MBBS in India: What to Do Next; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Ethiopian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Ghanaian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Malaysian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nepali Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sudanese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Zimbabwean Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; Urology in the UKMLA: High-Yield Topics for the AKT; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Care of the Elderly and Frailty in the UKMLA: What to Revise; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Genetics and Genomics in the UKMLA: What You Need to Know; The GMC Annual Retention Fee, Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Medical Statistics and Evidence-Based Medicine in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; The Multi-Specialty Recruitment Assessment (MSRA), Explained; NICE Guidelines and the AKT: What You Actually Need to Know; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Substance Misuse and Addiction in the UKMLA: What to Revise; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Care of the Elderly and Frailty in the UKMLA: What to Revise; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Genetics and Genomics in the UKMLA: What You Need to Know; The GMC Annual Retention Fee, Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Medical Statistics and Evidence-Based Medicine in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; The Multi-Specialty Recruitment Assessment (MSRA), Explained; NICE Guidelines and the AKT: What You Actually Need to Know; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Substance Misuse and Addiction in the UKMLA: What to Revise; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Prepare for the UKMLA as a UK Final-Year Student; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -639,14 +639,14 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ARCP: The Annual Review of Competence Progression, Explained; Breaking Bad News in the CPSA: A Complete Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The GMC Annual Retention Fee, Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; Medically Unexplained Symptoms in the UKMLA: What to Revise; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Write UKMLA Revision Notes That Actually Work; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Breaking Bad News in the CPSA: A Complete Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; The GMC Annual Retention Fee, Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Pass the UKMLA on Your First Attempt; Medically Unexplained Symptoms in the UKMLA: What to Revise; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; How to Prepare for the UKMLA as a UK Final-Year Student; How to Write UKMLA Revision Notes That Actually Work; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -674,14 +674,14 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The GMC Annual Retention Fee, Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Indemnity Insurance for Doctors, Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; The NHS Pension Scheme for Doctors, Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Understanding NHS Pay Scales and Banding for Doctors; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; Cost of GMC Registration 2026: Full Fee Breakdown; The GMC Annual Retention Fee, Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Indemnity Insurance for Doctors, Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; The NHS Pension Scheme for Doctors, Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Ethiopian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Ghanaian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Malaysian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nepali Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sudanese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Zimbabwean Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Understanding NHS Pay Scales and Banding for Doctors; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -709,14 +709,14 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Prepare for the UKMLA as a UK Final-Year Student; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -744,14 +744,14 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Early Pregnancy Complications in the UKMLA: The Essential Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Genetics and Genomics in the UKMLA: What You Need to Know; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Early Pregnancy Complications in the UKMLA: The Essential Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Genetics and Genomics in the UKMLA: What You Need to Know; GMC EPIC/MyIntealth Verification Process Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -779,14 +779,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Breaking Bad News in the CPSA: A Complete Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Genetics and Genomics in the UKMLA: What You Need to Know; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Gynaecological Cancers in the UKMLA: Red Flags and Referral; The History of the UKMLA and PLAB Transition, Explained; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How to Write an NHS CV and Application That Gets Shortlisted; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; The Multi-Specialty Recruitment Assessment (MSRA), Explained; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; OET vs IELTS for GMC Registration: Which Should You Take?; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Public Health and Screening in the UKMLA: What You Need to Know; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Breaking Bad News in the CPSA: A Complete Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Genetics and Genomics in the UKMLA: What You Need to Know; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Gynaecological Cancers in the UKMLA: Red Flags and Referral; The History of the UKMLA and PLAB Transition, Explained; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; How to Write an NHS CV and Application That Gets Shortlisted; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; The Multi-Specialty Recruitment Assessment (MSRA), Explained; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; OET vs IELTS for GMC Registration: Which Should You Take?; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Public Health and Screening in the UKMLA: What You Need to Know; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA After MBBS in India: What to Do Next; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nepali Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Zimbabwean Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Prepare for the UKMLA as a UK Final-Year Student; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -814,14 +814,14 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>ARCP: The Annual Review of Competence Progression, Explained; The Certificate of Completion of Training (CCT), Explained; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; The History of the UKMLA and PLAB Transition, Explained; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Write an NHS CV and Application That Gets Shortlisted; Indemnity Insurance for Doctors, Explained; The Internship Requirement for GMC Registration, Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Locum vs Substantive NHS Posts: Which Is Right for You?; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The NHS e-Portfolio: A Practical Guide for Doctors; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; OET vs IELTS for GMC Registration: Which Should You Take?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Transgender Health in the UKMLA: What the Content Map Covers; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; How UK Medical Schools Implement the UKMLA: An Overview; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; The Certificate of Completion of Training (CCT), Explained; Cost of GMC Registration 2026: Full Fee Breakdown; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC EPIC/MyIntealth Verification Process Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; The History of the UKMLA and PLAB Transition, Explained; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Write an NHS CV and Application That Gets Shortlisted; Indemnity Insurance for Doctors, Explained; The Internship Requirement for GMC Registration, Explained; Is UKMLA Replacing PLAB? The Real Relationship, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Locum vs Substantive NHS Posts: Which Is Right for You?; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The NHS e-Portfolio: A Practical Guide for Doctors; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; OET vs IELTS for GMC Registration: Which Should You Take?; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Transgender Health in the UKMLA: What the Content Map Covers; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; How UK Medical Schools Implement the UKMLA: An Overview; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sudanese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Special Circumstances: Accommodations Beyond Disability Access; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -884,14 +884,14 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Breaking Bad News in the CPSA: A Complete Guide; Cardiology High-Yield Topics for the UKMLA AKT; Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Domestic Abuse and Adult Safeguarding in the UKMLA; Early Pregnancy Complications in the UKMLA: The Essential Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Genetics and Genomics in the UKMLA: What You Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Gynaecological Cancers in the UKMLA: Red Flags and Referral; The History of the UKMLA and PLAB Transition, Explained; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Immunology and Allergy in the UKMLA: High-Yield Revision; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Statistics and Evidence-Based Medicine in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Public Health and Screening in the UKMLA: What You Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Substance Misuse and Addiction in the UKMLA: What to Revise; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Breaking Bad News in the CPSA: A Complete Guide; Cardiology High-Yield Topics for the UKMLA AKT; Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Domestic Abuse and Adult Safeguarding in the UKMLA; Early Pregnancy Complications in the UKMLA: The Essential Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Genetics and Genomics in the UKMLA: What You Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Group Study vs Solo Study for the UKMLA: What Works Best?; Gynaecological Cancers in the UKMLA: Red Flags and Referral; The History of the UKMLA and PLAB Transition, Explained; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Immunology and Allergy in the UKMLA: High-Yield Revision; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Medical Statistics and Evidence-Based Medicine in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Public Health and Screening in the UKMLA: What You Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Substance Misuse and Addiction in the UKMLA: What to Revise; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -1104,12 +1104,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>/news#blood-tests-data-interpretation-akt</t>
+          <t>/news#best-ukmla-question-banks-compared</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1118,41 +1118,41 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Medical Statistics and Evidence-Based Medicine in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>How to Prepare for the UKMLA as a UK Final-Year Student; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>Eligibility; AKT Exam Pattern; Fees; Preparation; MLA Content Map / Syllabus; Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; MLA Content Map: The Blueprint Behind Every UKMLA Question; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Prepare for the UKMLA as a UK Final-Year Student; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Breaking Bad News in the CPSA: A Complete Guide</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>/news#breaking-bad-news-in-the-cpsa</t>
+          <t>/news#blood-tests-data-interpretation-akt</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1160,42 +1160,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>1</v>
+      <c r="D19" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Medical Statistics and Evidence-Based Medicine in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; Clinical Examination Stations in the CPSA: A Practical Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; The History of the UKMLA and PLAB Transition, Explained; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors</t>
+          <t>Breaking Bad News in the CPSA: A Complete Guide</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>/news#bringing-family-to-uk-dependent-visa-guide</t>
+          <t>/news#breaking-bad-news-in-the-cpsa</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1203,42 +1203,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n">
-        <v>2</v>
+      <c r="D20" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Relocating to the UK: A Practical Guide for IMG Doctors</t>
+          <t>UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>Eligibility; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; Clinical Examination Stations in the CPSA: A Practical Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; The History of the UKMLA and PLAB Transition, Explained; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>/news#cardiology-ukmla-akt-revision</t>
+          <t>/news#bringing-family-to-uk-dependent-visa-guide</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1247,41 +1247,41 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Relocating to the UK: A Practical Guide for IMG Doctors</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>/news#care-of-the-elderly-and-frailty-ukmla</t>
+          <t>/news#cardiology-ukmla-akt-revision</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1290,19 +1290,19 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Public Health and Screening in the UKMLA: What You Need to Know; Urology in the UKMLA: High-Yield Topics for the AKT</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; MLA Content Map / Syllabus; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Public Health and Screening in the UKMLA: What You Need to Know; Urology in the UKMLA: High-Yield Topics for the AKT</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1319,12 +1319,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>The Certificate of Completion of Training (CCT), Explained</t>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>/news#certificate-of-completion-of-training-cct-explained</t>
+          <t>/news#care-of-the-elderly-and-frailty-ukmla</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1340,34 +1340,34 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>ARCP: The Annual Review of Competence Progression, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
+          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Public Health and Screening in the UKMLA: What You Need to Know; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; ARCP: The Annual Review of Competence Progression, Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The GMC Revalidation Process, Explained for New Doctors; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Multi-Specialty Recruitment Assessment (MSRA), Explained; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>AKT Exam Pattern; MLA Content Map / Syllabus; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Public Health and Screening in the UKMLA: What You Need to Know; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Chronic Pain Management in the UKMLA: What to Revise</t>
+          <t>The Certificate of Completion of Training (CCT), Explained</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>/news#chronic-pain-management-ukmla</t>
+          <t>/news#certificate-of-completion-of-training-cct-explained</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1376,41 +1376,41 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Immunology and Allergy in the UKMLA: High-Yield Revision</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
+          <t>Registration Guide; ARCP: The Annual Review of Competence Progression, Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The GMC Revalidation Process, Explained for New Doctors; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Multi-Specialty Recruitment Assessment (MSRA), Explained; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
+          <t>Chronic Pain Management in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>/news#clinical-examination-cpsa-guide</t>
+          <t>/news#chronic-pain-management-ukmla</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1419,41 +1419,41 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Immunology and Allergy in the UKMLA: High-Yield Revision</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Preparation; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>MLA Content Map / Syllabus; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>/news#consent-and-mental-capacity-ukmla</t>
+          <t>/news#clinical-examination-cpsa-guide</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1462,41 +1462,41 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Domestic Abuse and Adult Safeguarding in the UKMLA; Medical Statistics and Evidence-Based Medicine in the UKMLA; Transgender Health in the UKMLA: What the Content Map Covers</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern; MLA Content Map / Syllabus; Domestic Abuse and Adult Safeguarding in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide; Transgender Health in the UKMLA: What the Content Map Covers</t>
+          <t>Preparation; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>/news#contraception-counselling-ukmla</t>
+          <t>/news#consent-and-mental-capacity-ukmla</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1505,19 +1505,19 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide; Menopause Management in the UKMLA: What You Need to Know</t>
+          <t>Domestic Abuse and Adult Safeguarding in the UKMLA; Medical Statistics and Evidence-Based Medicine in the UKMLA; Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern; MLA Content Map / Syllabus; Early Pregnancy Complications in the UKMLA: The Essential Guide; Menopause Management in the UKMLA: What You Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations</t>
+          <t>CPSA Exam Pattern; MLA Content Map / Syllabus; Domestic Abuse and Adult Safeguarding in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide; Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient</t>
+          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>/news#critical-care-and-intensive-care-basics-ukmla</t>
+          <t>/news#contraception-counselling-ukmla</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1547,20 +1547,20 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
-        <v>1</v>
+      <c r="D28" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Substance Misuse and Addiction in the UKMLA: What to Revise</t>
+          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide; Menopause Management in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus; Chronic Pain Management in the UKMLA: What to Revise; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Substance Misuse and Addiction in the UKMLA: What to Revise; Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>CPSA Exam Pattern; MLA Content Map / Syllabus; Early Pregnancy Complications in the UKMLA: The Essential Guide; Menopause Management in the UKMLA: What You Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know</t>
+          <t>Cost of GMC Registration 2026: Full Fee Breakdown</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>/news#dermatology-ukmla-revision</t>
+          <t>/news#cost-of-gmc-registration-2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1591,41 +1591,41 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>GMC EPIC/MyIntealth Verification Process Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Fees; Registration Guide; GMC EPIC/MyIntealth Verification Process Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration for EU and Irish Doctors: What Changed After Brexit; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>/news#disability-access-ukmla-guide</t>
+          <t>/news#critical-care-and-intensive-care-basics-ukmla</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1633,42 +1633,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n">
-        <v>13</v>
+      <c r="D30" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+          <t>Substance Misuse and Addiction in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; UKMLA vs PLAB; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>MLA Content Map / Syllabus; Chronic Pain Management in the UKMLA: What to Revise; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Substance Misuse and Addiction in the UKMLA: What to Revise; Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Appeals and Resits</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Domestic Abuse and Adult Safeguarding in the UKMLA</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>/news#domestic-abuse-and-safeguarding-adults-ukmla</t>
+          <t>/news#dermatology-ukmla-revision</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1677,19 +1677,19 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Medically Unexplained Symptoms in the UKMLA: What to Revise; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus; Consent and Mental Capacity in the UKMLA: The Complete Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Medically Unexplained Symptoms in the UKMLA: What to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>/news#early-pregnancy-complications-ukmla</t>
+          <t>/news#disability-access-ukmla-guide</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1720,41 +1720,41 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Menopause Management in the UKMLA: What You Need to Know</t>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; Contraception Counselling in the UKMLA: A Complete Revision Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; UKMLA vs PLAB; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Appeals and Resits</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise</t>
+          <t>Domestic Abuse and Adult Safeguarding in the UKMLA</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>/news#ecg-interpretation-ukmla</t>
+          <t>/news#domestic-abuse-and-safeguarding-adults-ukmla</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1763,19 +1763,19 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Medically Unexplained Symptoms in the UKMLA: What to Revise; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>MLA Content Map / Syllabus; Consent and Mental Capacity in the UKMLA: The Complete Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Medically Unexplained Symptoms in the UKMLA: What to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Emergency Medicine and Acute Presentations in the UKMLA</t>
+          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>/news#emergency-medicine-ukmla-revision</t>
+          <t>/news#early-pregnancy-complications-ukmla</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1806,19 +1806,19 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Early Pregnancy Complications in the UKMLA: The Essential Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Immunology and Allergy in the UKMLA: High-Yield Revision; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
+          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Menopause Management in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; Contraception Counselling in the UKMLA: A Complete Revision Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
+          <t>ECG Interpretation for the UKMLA: The Findings You Must Recognise</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>/news#endocrinology-diabetes-ukmla-revision</t>
+          <t>/news#ecg-interpretation-ukmla</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Menopause Management in the UKMLA: What You Need to Know; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
+          <t>Emergency Medicine and Acute Presentations in the UKMLA</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>/news#english-language-requirement-for-ukmla-india</t>
+          <t>/news#emergency-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1895,38 +1895,38 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Early Pregnancy Complications in the UKMLA: The Essential Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Immunology and Allergy in the UKMLA: High-Yield Revision; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>AKT Exam Pattern; Preparation; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Working Hours and Rest Rules for Doctors: The EWTD Explained</t>
+          <t>Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>/news#ewtd-working-hours-and-rest-rules-for-doctors</t>
+          <t>/news#endocrinology-diabetes-ukmla-revision</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1935,41 +1935,41 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>ARCP: The Annual Review of Competence Progression, Explained; Locum vs Substantive NHS Posts: Which Is Right for You?; Understanding NHS Pay Scales and Banding for Doctors</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Menopause Management in the UKMLA: What You Need to Know; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; Registration Guide; ARCP: The Annual Review of Competence Progression, Explained; Understanding the Foundation Programme: What Awaits After the UKMLA; Locum vs Substantive NHS Posts: Which Is Right for You?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
+          <t>AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-programme-2026-recruitment-changes</t>
+          <t>/news#english-language-requirement-for-ukmla-india</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1978,24 +1978,24 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Regulation of Physician Associates: What Doctors Need to Know; The Multi-Specialty Recruitment Assessment (MSRA), Explained; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA After MBBS in India: What to Do Next; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nepali Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Key Dates; Preparation; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Eligibility; Official Resources; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
+          <t>Working Hours and Rest Rules for Doctors: The EWTD Explained</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-programme-after-ukmla</t>
+          <t>/news#ewtd-working-hours-and-rest-rules-for-doctors</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2021,37 +2021,41 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Indemnity Insurance for Doctors, Explained; The Internship Requirement for GMC Registration, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; Relocating to the UK: A Practical Guide for IMG Doctors; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Locum vs Substantive NHS Posts: Which Is Right for You?; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Eligibility; Official Resources; Registration Guide; ARCP: The Annual Review of Competence Progression, Explained; Understanding the Foundation Programme: What Awaits After the UKMLA; Locum vs Substantive NHS Posts: Which Is Right for You?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Uncategorised</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t>Registration &amp; Eligibility</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
+          <t>/news#foundation-programme-2026-recruitment-changes</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2060,24 +2064,24 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>10</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>The Certificate of Completion of Training (CCT), Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Regulation of Physician Associates: What Doctors Need to Know; The Multi-Specialty Recruitment Assessment (MSRA), Explained; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Key Dates; Preparation; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2089,12 +2093,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
+          <t>Understanding the Foundation Programme: What Awaits After the UKMLA</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>/news#gastroenterology-ukmla-akt-revision</t>
+          <t>/news#foundation-programme-after-ukmla</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2103,41 +2107,37 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; Working Hours and Rest Rules for Doctors: The EWTD Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Indemnity Insurance for Doctors, Explained; The Internship Requirement for GMC Registration, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; MLA Content Map: The Blueprint Behind Every UKMLA Question; Relocating to the UK: A Practical Guide for IMG Doctors; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Prepare for the UKMLA as a UK Final-Year Student; UKMLA Results: How to Interpret Your Feedback Report; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
+          <t>Uncategorised</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Genetics and Genomics in the UKMLA: What You Need to Know</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>/news#genetics-and-genomics-in-the-ukmla</t>
+          <t>/news#foundation-year-vs-specialty-training-for-imgs</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2146,41 +2146,41 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>10</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Sepsis Recognition and Management in the UKMLA: The Essential Guide; Transgender Health in the UKMLA: What the Content Map Covers</t>
+          <t>The Certificate of Completion of Training (CCT), Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The Multi-Specialty Recruitment Assessment (MSRA), Explained; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; How to Prepare for the UKMLA as a UK Final-Year Student</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>The GMC Annual Retention Fee, Explained</t>
+          <t>Gastroenterology and Hepatology in the UKMLA AKT</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-annual-retention-fee-explained</t>
+          <t>/news#gastroenterology-ukmla-akt-revision</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2189,41 +2189,41 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>The NHS e-Portfolio: A Practical Guide for Doctors; The NHS Pension Scheme for Doctors, Explained; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Fees; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
+          <t>Genetics and Genomics in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-english-language-exemption-for-imgs</t>
+          <t>/news#genetics-and-genomics-in-the-ukmla</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2232,41 +2232,41 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Sepsis Recognition and Management in the UKMLA: The Essential Guide; Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>AKT Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
+          <t>The GMC Annual Retention Fee, Explained</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
+          <t>/news#gmc-annual-retention-fee-explained</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2275,41 +2275,41 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Indemnity Insurance for Doctors, Explained</t>
+          <t>The NHS e-Portfolio: A Practical Guide for Doctors; The NHS Pension Scheme for Doctors, Explained; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Fees; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
+          <t>/news#gmc-english-language-exemption-for-imgs</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2318,19 +2318,19 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>Eligibility; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration Requirements for International Doctors: The Complete Process; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2340,19 +2340,19 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
+          <t>GMC EPIC/MyIntealth Verification Process Explained</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-recognised-primary-medical-qualifications</t>
+          <t>/news#gmc-epic-verification-process-explained</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2364,16 +2364,16 @@
         <v>7</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; The Internship Requirement for GMC Registration, Explained; OET vs IELTS for GMC Registration: Which Should You Take?; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Cost of GMC Registration 2026: Full Fee Breakdown; UKMLA for Ethiopian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Ghanaian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Malaysian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nepali Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sudanese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Zimbabwean Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>Eligibility; Official Resources; Registration Guide; Cost of GMC Registration 2026: Full Fee Breakdown; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2383,19 +2383,19 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-and-epic-verification-india</t>
+          <t>/news#gmc-fitness-to-practise-explained-for-new-doctors</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2404,24 +2404,24 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Indemnity Insurance for Doctors, Explained</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Good Medical Practice and the UKMLA: What the GMC Expects; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2433,12 +2433,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-for-eu-and-irish-doctors</t>
+          <t>/news#gmc-order-reform-2026-protected-medical-titles</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2447,41 +2447,41 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; GMC Regulation of Physician Associates: What Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-refund-policy</t>
+          <t>/news#gmc-recognised-primary-medical-qualifications</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2490,19 +2490,19 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The GMC Annual Retention Fee, Explained; How Long Does GMC Registration Take? A Realistic Timeline; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; The Internship Requirement for GMC Registration, Explained; OET vs IELTS for GMC Registration: Which Should You Take?; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Fees; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Eligibility; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; The Internship Requirement for GMC Registration, Explained; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-registration-requirements-for-international-doctors</t>
+          <t>/news#gmc-registration-and-epic-verification-india</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2533,19 +2533,19 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; Relocating to the UK: A Practical Guide for IMG Doctors; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>Cost of GMC Registration 2026: Full Fee Breakdown; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC EPIC/MyIntealth Verification Process Explained; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; UKMLA After MBBS in India: What to Do Next; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Eligibility; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
+          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
+          <t>/news#gmc-registration-for-eu-and-irish-doctors</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2576,41 +2576,41 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors</t>
+          <t>Cost of GMC Registration 2026: Full Fee Breakdown; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; Good Medical Practice and the UKMLA: What the GMC Expects; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>Eligibility; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>The GMC Revalidation Process, Explained for New Doctors</t>
+          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-revalidation-process-explained</t>
+          <t>/news#gmc-registration-refund-policy</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2619,41 +2619,41 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>The Certificate of Completion of Training (CCT), Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; The NHS e-Portfolio: A Practical Guide for Doctors; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; The GMC Annual Retention Fee, Explained; How Long Does GMC Registration Take? A Realistic Timeline; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Fees; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
+          <t>GMC Registration Requirements for International Doctors: The Complete Process</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
+          <t>/news#gmc-registration-requirements-for-international-doctors</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2662,24 +2662,24 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; OET vs IELTS for GMC Registration: Which Should You Take?; Relocating to the UK: A Practical Guide for IMG Doctors; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+          <t>Cost of GMC Registration 2026: Full Fee Breakdown; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC EPIC/MyIntealth Verification Process Explained; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; OET vs IELTS for GMC Registration: Which Should You Take?; Relocating to the UK: A Practical Guide for IMG Doctors; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Ethiopian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Ghanaian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Malaysian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nepali Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sudanese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Zimbabwean Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Preparation; Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Eligibility: Who Can Sit the Exam?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2691,12 +2691,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
+          <t>GMC Regulation of Physician Associates: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>/news#good-medical-practice-ukmla</t>
+          <t>/news#gmc-regulation-of-physician-associates-what-doctors-need-to-know</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2705,19 +2705,19 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Domestic Abuse and Adult Safeguarding in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; Indemnity Insurance for Doctors, Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; AKT Exam Pattern; Registration Guide; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The GMC Revalidation Process, Explained for New Doctors; Good Medical Practice and the UKMLA: What the GMC Expects; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2725,17 +2725,21 @@
           <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Registration Guide</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
+          <t>The GMC Revalidation Process, Explained for New Doctors</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>/news#group-study-vs-solo-ukmla</t>
+          <t>/news#gmc-revalidation-process-explained</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2744,41 +2748,41 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>The Certificate of Completion of Training (CCT), Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; The NHS e-Portfolio: A Practical Guide for Doctors; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Professional Practice &amp; Safety</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Gynaecological Cancers in the UKMLA: Red Flags and Referral</t>
+          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>/news#gynaecological-cancers-ukmla</t>
+          <t>/news#gmc-welcome-to-uk-practice-induction-guide</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2787,41 +2791,41 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide; Public Health and Screening in the UKMLA: What You Need to Know</t>
+          <t>GMC Fitness to Practise Explained: What New Doctors Need to Know; OET vs IELTS for GMC Registration: Which Should You Take?; Relocating to the UK: A Practical Guide for IMG Doctors; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Medical Statistics and Evidence-Based Medicine in the UKMLA; Menopause Management in the UKMLA: What You Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Preparation; Registration Guide; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Registration Requirements for International Doctors: The Complete Process; OET vs IELTS for GMC Registration: Which Should You Take?; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
+          <t>Good Medical Practice and the UKMLA: What the GMC Expects</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>/news#haematology-ukmla-revision</t>
+          <t>/news#good-medical-practice-ukmla</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2830,41 +2834,37 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Genetics and Genomics in the UKMLA: What You Need to Know; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Domestic Abuse and Adult Safeguarding in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; The GMC Revalidation Process, Explained for New Doctors; Indemnity Insurance for Doctors, Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>The History of the UKMLA and PLAB Transition, Explained</t>
+          <t>Group Study vs Solo Study for the UKMLA: What Works Best?</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>/news#history-of-ukmla-plab-transition-explained</t>
+          <t>/news#group-study-vs-solo-ukmla</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2872,42 +2872,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D59" s="4" t="n">
-        <v>1</v>
+      <c r="D59" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Breaking Bad News in the CPSA: A Complete Guide</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; How to Prepare for the UKMLA as a UK Final-Year Student; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA Exam Day: What to Expect at the AKT and CPSA; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Key Dates and Sitting Schedule: What to Know; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA?</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
+          <t>Gynaecological Cancers in the UKMLA: Red Flags and Referral</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>/news#how-long-does-gmc-registration-take</t>
+          <t>/news#gynaecological-cancers-ukmla</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2916,41 +2916,41 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
+          <t>Early Pregnancy Complications in the UKMLA: The Essential Guide; Public Health and Screening in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Medical Statistics and Evidence-Based Medicine in the UKMLA; Menopause Management in the UKMLA: What You Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
+          <t>Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
+          <t>/news#haematology-ukmla-revision</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -2959,41 +2959,41 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>Genetics and Genomics in the UKMLA: What You Need to Know; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
+          <t>The History of the UKMLA and PLAB Transition, Explained</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
+          <t>/news#history-of-ukmla-plab-transition-explained</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3001,42 +3001,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n">
-        <v>23</v>
+      <c r="D62" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Breaking Bad News in the CPSA: A Complete Guide</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Eligibility; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA Exam Day: What to Expect at the AKT and CPSA; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>How to Pass the UKMLA on Your First Attempt</t>
+          <t>How Long Does GMC Registration Take? A Realistic Timeline</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
+          <t>/news#how-long-does-gmc-registration-take</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3045,41 +3045,41 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Cost of GMC Registration 2026: Full Fee Breakdown; GMC EPIC/MyIntealth Verification Process Explained; GMC Registration for EU and Irish Doctors: What Changed After Brexit; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Resits: Rules, Limits, and How to Bounce Back; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
+          <t>How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-read-akt-stem</t>
+          <t>/news#how-to-become-a-doctor-in-the-uk-gmc-registration-guide</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3091,38 +3091,38 @@
         <v>13</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Cost of GMC Registration 2026: Full Fee Breakdown; GMC EPIC/MyIntealth Verification Process Explained; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; The Internship Requirement for GMC Registration, Explained; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-register-plab-1</t>
+          <t>/news#how-to-become-a-doctor-in-uk-from-india</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3131,41 +3131,41 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA After MBBS in India: What to Do Next; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA After MBBS in India: What to Do Next; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>How to Write an NHS CV and Application That Gets Shortlisted</t>
+          <t>How to Pass the UKMLA on Your First Attempt</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>/news#how-to-write-an-nhs-cv-and-application</t>
+          <t>/news#how-to-pass-ukmla-on-first-attempt</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3173,42 +3173,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D66" s="4" t="n">
-        <v>1</v>
+      <c r="D66" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Preparation; Registration Guide; Locum vs Substantive NHS Posts: Which Is Right for You?; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Relocating to the UK: A Practical Guide for IMG Doctors; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Group Study vs Solo Study for the UKMLA: What Works Best?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Resits: Rules, Limits, and How to Bounce Back; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Immunology and Allergy in the UKMLA: High-Yield Revision</t>
+          <t>How to Read an AKT Stem: Avoiding Common Traps</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>/news#immunology-and-allergy-ukmla</t>
+          <t>/news#how-to-read-akt-stem</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3216,42 +3216,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D67" s="4" t="n">
-        <v>1</v>
+      <c r="D67" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus; Chronic Pain Management in the UKMLA: What to Revise; Emergency Medicine and Acute Presentations in the UKMLA; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Indemnity Insurance for Doctors, Explained</t>
+          <t>How to Register for PLAB 1: A Step-by-Step Guide for IMGs</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>/news#indemnity-insurance-for-doctors-explained</t>
+          <t>/news#how-to-register-plab-1</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3259,20 +3259,20 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D68" s="4" t="n">
-        <v>1</v>
+      <c r="D68" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>The NHS Pension Scheme for Doctors, Explained</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; The NHS Pension Scheme for Doctors, Explained; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; Key Dates; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Key Dates and Sitting Schedule: What to Know</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3282,19 +3282,19 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
+          <t>How to Write an NHS CV and Application That Gets Shortlisted</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>/news#infection-microbiology-ukmla-revision</t>
+          <t>/news#how-to-write-an-nhs-cv-and-application</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3302,42 +3302,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D69" s="2" t="n">
-        <v>27</v>
+      <c r="D69" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Preparation; Registration Guide; Locum vs Substantive NHS Posts: Which Is Right for You?; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Relocating to the UK: A Practical Guide for IMG Doctors; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>The Internship Requirement for GMC Registration, Explained</t>
+          <t>Immunology and Allergy in the UKMLA: High-Yield Revision</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>/news#internship-requirement-for-gmc-registration</t>
+          <t>/news#immunology-and-allergy-ukmla</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -3345,42 +3345,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D70" s="2" t="n">
-        <v>2</v>
+      <c r="D70" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline</t>
+          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>MLA Content Map / Syllabus; Chronic Pain Management in the UKMLA: What to Revise; Emergency Medicine and Acute Presentations in the UKMLA; Nutrition and Metabolic Disorders in the UKMLA: What to Revise; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
+          <t>Indemnity Insurance for Doctors, Explained</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>/news#is-indian-mbbs-valid-in-uk</t>
+          <t>/news#indemnity-insurance-for-doctors-explained</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -3388,42 +3388,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
-        <v>7</v>
+      <c r="D71" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>The NHS Pension Scheme for Doctors, Explained</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; What Is the UKMLA?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Eligibility; Fees; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; The NHS Pension Scheme for Doctors, Explained; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
+          <t>Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>/news#is-ukmla-replacing-plab-explained</t>
+          <t>/news#infection-microbiology-ukmla-revision</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -3432,41 +3432,41 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>The History of the UKMLA and PLAB Transition, Explained; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Preparation; Gastroenterology and Hepatology in the UKMLA AKT; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained</t>
+          <t>The Internship Requirement for GMC Registration, Explained</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>/news#joining-a-royal-college-mrcp-mrcs-mrcgp-overview</t>
+          <t>/news#internship-requirement-for-gmc-registration</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -3478,38 +3478,38 @@
         <v>3</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; The Certificate of Completion of Training (CCT), Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
+          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; The Certificate of Completion of Training (CCT), Explained; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>Eligibility; Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
+          <t>/news#is-indian-mbbs-valid-in-uk</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -3518,41 +3518,41 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>The Certificate of Completion of Training (CCT), Explained; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How Long Does GMC Registration Take? A Realistic Timeline; Locum vs Substantive NHS Posts: Which Is Right for You?; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Official Resources; What Is the UKMLA?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Locum vs Substantive NHS Posts: Which Is Right for You?</t>
+          <t>Is UKMLA Replacing PLAB? The Real Relationship, Explained</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>/news#locum-vs-substantive-nhs-posts-explained</t>
+          <t>/news#is-ukmla-replacing-plab-explained</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -3561,41 +3561,41 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>ARCP: The Annual Review of Competence Progression, Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; How to Write an NHS CV and Application That Gets Shortlisted; The NHS e-Portfolio: A Practical Guide for Doctors</t>
+          <t>The History of the UKMLA and PLAB Transition, Explained; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Working Hours and Rest Rules for Doctors: The EWTD Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The NHS e-Portfolio: A Practical Guide for Doctors; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Fees; Registration Guide; UKMLA vs PLAB; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; PLAB 2 Preparation: How to Excel in the Clinical Assessment; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
+          <t>Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>/news#managing-ukmla-exam-anxiety</t>
+          <t>/news#joining-a-royal-college-mrcp-mrcs-mrcgp-overview</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -3604,41 +3604,41 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Breaking Bad News in the CPSA: A Complete Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Working Hours and Rest Rules for Doctors: The EWTD Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Pass the UKMLA on Your First Attempt; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Special Circumstances: Accommodations Beyond Disability Access; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; The Certificate of Completion of Training (CCT), Explained; The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>Preparation; What Is an Angoff Standard Setting and Why Does It Matter?; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Registration Guide; Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; The Certificate of Completion of Training (CCT), Explained; Understanding the Foundation Programme: What Awaits After the UKMLA; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
+          <t>Locally Employed Doctors: The Route to Full and Specialist GMC Registration</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>/news#mbbs-in-uk-for-indian-students</t>
+          <t>/news#locally-employed-doctors-route-to-gmc-registration</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -3647,41 +3647,41 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>The Certificate of Completion of Training (CCT), Explained; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How Long Does GMC Registration Take? A Realistic Timeline; Locum vs Substantive NHS Posts: Which Is Right for You?; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; MLA Content Map / Syllabus; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration Requirements for International Doctors: The Complete Process; How Long Does GMC Registration Take? A Realistic Timeline; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Medical Statistics and Evidence-Based Medicine in the UKMLA</t>
+          <t>Locum vs Substantive NHS Posts: Which Is Right for You?</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>/news#medical-statistics-and-evidence-based-medicine-ukmla</t>
+          <t>/news#locum-vs-substantive-nhs-posts-explained</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -3690,41 +3690,41 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Gynaecological Cancers in the UKMLA: Red Flags and Referral; Public Health and Screening in the UKMLA: What You Need to Know</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Working Hours and Rest Rules for Doctors: The EWTD Explained; How to Write an NHS CV and Application That Gets Shortlisted; The NHS e-Portfolio: A Practical Guide for Doctors</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; MLA Content Map / Syllabus; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Public Health and Screening in the UKMLA: What You Need to Know</t>
+          <t>Eligibility; Registration Guide; Working Hours and Rest Rules for Doctors: The EWTD Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The NHS e-Portfolio: A Practical Guide for Doctors; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
+          <t>Managing UKMLA Exam Anxiety: Practical Strategies for Candidates</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>/news#medical-training-initiative-scheme-closure-2026</t>
+          <t>/news#managing-ukmla-exam-anxiety</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -3733,41 +3733,41 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>GMC Regulation of Physician Associates: What Doctors Need to Know; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; Breaking Bad News in the CPSA: A Complete Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Working Hours and Rest Rules for Doctors: The EWTD Explained; GMC Fitness to Practise Explained: What New Doctors Need to Know; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Pass the UKMLA on Your First Attempt; UKMLA AKT Pass Mark and Pass Rate Explained; How to Prepare for the UKMLA as a UK Final-Year Student; UKMLA Special Circumstances: Accommodations Beyond Disability Access; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Preparation; What Is an Angoff Standard Setting and Why Does It Matter?; Group Study vs Solo Study for the UKMLA: What Works Best?; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
+          <t>MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
+          <t>/news#mbbs-in-uk-for-indian-students</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -3776,19 +3776,19 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Fees; MLA Content Map / Syllabus; What Is the UKMLA?; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -3805,12 +3805,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Medically Unexplained Symptoms in the UKMLA: What to Revise</t>
+          <t>Medical Statistics and Evidence-Based Medicine in the UKMLA</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>/news#medically-unexplained-symptoms-ukmla</t>
+          <t>/news#medical-statistics-and-evidence-based-medicine-ukmla</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -3822,16 +3822,16 @@
         <v>2</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Domestic Abuse and Adult Safeguarding in the UKMLA; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
+          <t>Gynaecological Cancers in the UKMLA: Red Flags and Referral; Public Health and Screening in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Domestic Abuse and Adult Safeguarding in the UKMLA; Mental Health Presentations in the UKMLA: What to Revise; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations</t>
+          <t>AKT Exam Pattern; MLA Content Map / Syllabus; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Public Health and Screening in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Menopause Management in the UKMLA: What You Need to Know</t>
+          <t>Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>/news#menopause-management-ukmla</t>
+          <t>/news#medical-training-initiative-scheme-closure-2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -3862,41 +3862,41 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide; Gynaecological Cancers in the UKMLA: Red Flags and Referral</t>
+          <t>GMC Regulation of Physician Associates: What Doctors Need to Know; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Contraception Counselling in the UKMLA: A Complete Revision Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Eligibility; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
+          <t>The Medical Training Prioritisation Act 2026: What It Means for IMGs</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>/news#mental-health-ukmla-revision</t>
+          <t>/news#medical-training-prioritisation-act-2026-imgs</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -3905,41 +3905,41 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Medically Unexplained Symptoms in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Substance Misuse and Addiction in the UKMLA: What to Revise; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>Eligibility; Registration Guide; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
+          <t>Medically Unexplained Symptoms in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>/news#mla-content-map-explained</t>
+          <t>/news#medically-unexplained-symptoms-ukmla</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -3948,24 +3948,24 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Genetics and Genomics in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Domestic Abuse and Adult Safeguarding in the UKMLA; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Domestic Abuse and Adult Safeguarding in the UKMLA; Mental Health Presentations in the UKMLA: What to Revise; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>The Role of Mock Exams in UKMLA Preparation</t>
+          <t>Menopause Management in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>/news#mock-exams-ukmla-preparation</t>
+          <t>/news#menopause-management-ukmla</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -3991,41 +3991,41 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Breaking Bad News in the CPSA: A Complete Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
+          <t>Contraception Counselling in the UKMLA: A Complete Revision Guide; Gynaecological Cancers in the UKMLA: Red Flags and Referral</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Contraception Counselling in the UKMLA: A Complete Revision Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
+          <t>Mental Health Presentations in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>/news#multi-specialty-recruitment-assessment-msra-explained</t>
+          <t>/news#mental-health-ukmla-revision</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4034,41 +4034,41 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>ARCP: The Annual Review of Competence Progression, Explained; The Certificate of Completion of Training (CCT), Explained</t>
+          <t>Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Medically Unexplained Symptoms in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Psychiatry Communication Stations: Handling Difficult Conversations; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Substance Misuse and Addiction in the UKMLA: What to Revise; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; Preparation; ARCP: The Annual Review of Competence Progression, Explained; The Certificate of Completion of Training (CCT), Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Good Medical Practice and the UKMLA: What the GMC Expects; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>/news#nephrology-ukmla-revision</t>
+          <t>/news#mla-content-map-explained</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4077,24 +4077,24 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Genetics and Genomics in the UKMLA: What You Need to Know; NICE Guidelines and the AKT: What You Actually Need to Know; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; Urology in the UKMLA: High-Yield Topics for the AKT</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; Genetics and Genomics in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA After MBBS in India: What to Do Next; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; How to Prepare for the UKMLA as a UK Final-Year Student; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
+          <t>The Role of Mock Exams in UKMLA Preparation</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>/news#neurology-ukmla-revision</t>
+          <t>/news#mock-exams-ukmla-preparation</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4123,38 +4123,38 @@
         <v>16</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Breaking Bad News in the CPSA: A Complete Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs PLAB: What Is the Difference?</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>The NHS e-Portfolio: A Practical Guide for Doctors</t>
+          <t>The Multi-Specialty Recruitment Assessment (MSRA), Explained</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>/news#nhs-eportfolio-guide-for-doctors</t>
+          <t>/news#multi-specialty-recruitment-assessment-msra-explained</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -4163,24 +4163,24 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>ARCP: The Annual Review of Competence Progression, Explained; Locum vs Substantive NHS Posts: Which Is Right for You?</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; The Certificate of Completion of Training (CCT), Explained; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; ARCP: The Annual Review of Competence Progression, Explained; The GMC Annual Retention Fee, Explained; The GMC Revalidation Process, Explained for New Doctors; Locum vs Substantive NHS Posts: Which Is Right for You?; How to Write UKMLA Revision Notes That Actually Work; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; AKT Exam Pattern; Preparation; ARCP: The Annual Review of Competence Progression, Explained; The Certificate of Completion of Training (CCT), Explained; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; Good Medical Practice and the UKMLA: What the GMC Expects; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates</t>
+          <t>Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>/news#nhs-job-interview-preparation-guide</t>
+          <t>/news#nephrology-ukmla-revision</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4206,41 +4206,41 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>How to Write an NHS CV and Application That Gets Shortlisted; Relocating to the UK: A Practical Guide for IMG Doctors</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Genetics and Genomics in the UKMLA: What You Need to Know; NICE Guidelines and the AKT: What You Actually Need to Know; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Three Months to the UKMLA AKT: A Final Preparation Countdown; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Write an NHS CV and Application That Gets Shortlisted; Relocating to the UK: A Practical Guide for IMG Doctors; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>The NHS Pension Scheme for Doctors, Explained</t>
+          <t>Neurology in the UKMLA: High-Yield Topics and Revision Tips</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>/news#nhs-pension-scheme-for-doctors-explained</t>
+          <t>/news#neurology-ukmla-revision</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -4249,41 +4249,41 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Indemnity Insurance for Doctors, Explained; Understanding NHS Pay Scales and Banding for Doctors</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>Fees; The GMC Annual Retention Fee, Explained; Indemnity Insurance for Doctors, Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
+          <t>Preparation; MLA Content Map / Syllabus; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
+          <t>The NHS e-Portfolio: A Practical Guide for Doctors</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>/news#nice-guidelines-akt-revision</t>
+          <t>/news#nhs-eportfolio-guide-for-doctors</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -4292,41 +4292,41 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>ARCP: The Annual Review of Competence Progression, Explained; Locum vs Substantive NHS Posts: Which Is Right for You?</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Registration Guide; ARCP: The Annual Review of Competence Progression, Explained; The GMC Annual Retention Fee, Explained; The GMC Revalidation Process, Explained for New Doctors; Locum vs Substantive NHS Posts: Which Is Right for You?; How to Write UKMLA Revision Notes That Actually Work; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
+          <t>NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>/news#nutrition-and-metabolic-disorders-ukmla</t>
+          <t>/news#nhs-job-interview-preparation-guide</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -4334,42 +4334,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D93" s="4" t="n">
-        <v>1</v>
+      <c r="D93" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Immunology and Allergy in the UKMLA: High-Yield Revision</t>
+          <t>How to Write an NHS CV and Application That Gets Shortlisted; Relocating to the UK: A Practical Guide for IMG Doctors; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Care of the Elderly and Frailty in the UKMLA: What to Revise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Immunology and Allergy in the UKMLA: High-Yield Revision; Substance Misuse and Addiction in the UKMLA: What to Revise</t>
+          <t>Registration Guide; Good Medical Practice and the UKMLA: What the GMC Expects; How to Write an NHS CV and Application That Gets Shortlisted; Relocating to the UK: A Practical Guide for IMG Doctors; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
+          <t>The NHS Pension Scheme for Doctors, Explained</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
+          <t>/news#nhs-pension-scheme-for-doctors-explained</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -4378,41 +4378,41 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Contraception Counselling in the UKMLA: A Complete Revision Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Menopause Management in the UKMLA: What You Need to Know; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Indemnity Insurance for Doctors, Explained; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Fees; The GMC Annual Retention Fee, Explained; Indemnity Insurance for Doctors, Explained; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
+          <t>NICE Guidelines and the AKT: What You Actually Need to Know</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
+          <t>/news#nice-guidelines-akt-revision</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -4421,41 +4421,41 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; ECG Interpretation for the UKMLA: The Findings You Must Recognise; How to Read an AKT Stem: Avoiding Common Traps; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Preparation; Registration Guide; Results and Scoring; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Requirements for International Doctors: The Complete Process; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>AKT Exam Pattern; Preparation; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
+          <t>Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>/news#ophthalmology-ent-ukmla-revision</t>
+          <t>/news#nutrition-and-metabolic-disorders-ukmla</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -4463,20 +4463,20 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D96" s="2" t="n">
-        <v>11</v>
+      <c r="D96" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Immunology and Allergy in the UKMLA: High-Yield Revision</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; What Is the UKMLA?; Care of the Elderly and Frailty in the UKMLA: What to Revise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Immunology and Allergy in the UKMLA: High-Yield Revision; Substance Misuse and Addiction in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>/news#paediatrics-ukmla-revision</t>
+          <t>/news#obstetrics-gynaecology-ukmla-revision</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4507,19 +4507,19 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Contraception Counselling in the UKMLA: A Complete Revision Guide; Early Pregnancy Complications in the UKMLA: The Essential Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Menopause Management in the UKMLA: What You Need to Know; MLA Content Map: The Blueprint Behind Every UKMLA Question; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
+          <t>OET vs IELTS for GMC Registration: Which Should You Take?</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>/news#palliative-care-ukmla-revision</t>
+          <t>/news#oet-vs-ielts-for-gmc-registration-comparison</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -4550,41 +4550,41 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Eligibility; Preparation; Registration Guide; Results and Scoring; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; GMC Registration Requirements for International Doctors: The Complete Process; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>/news#patient-safety-ukmla-prescribing-errors</t>
+          <t>/news#ophthalmology-ent-ukmla-revision</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4593,37 +4593,41 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>11</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Menopause Management in the UKMLA: What You Need to Know; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Substance Misuse and Addiction in the UKMLA: What to Revise; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; Urology in the UKMLA: High-Yield Topics for the AKT; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>AKT Exam Pattern; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
+          <t>Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>/news#pharmacology-prescribing-safety-ukmla</t>
+          <t>/news#paediatrics-ukmla-revision</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -4632,19 +4636,19 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Immunology and Allergy in the UKMLA: High-Yield Revision; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Public Health and Screening in the UKMLA: What You Need to Know; Substance Misuse and Addiction in the UKMLA: What to Revise; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>CPSA Exam Pattern; Preparation; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -4661,12 +4665,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
+          <t>Palliative Care and End-of-Life Decisions in the UKMLA</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>/news#plab-2-preparation-guide</t>
+          <t>/news#palliative-care-ukmla-revision</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4675,41 +4679,41 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>UKMLA vs PLAB</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
+          <t>Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>/news#prescribing-in-renal-and-hepatic-impairment-ukmla</t>
+          <t>/news#patient-safety-ukmla-prescribing-errors</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -4718,41 +4722,37 @@
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Medically Unexplained Symptoms in the UKMLA: What to Revise</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Cardiology High-Yield Topics for the UKMLA AKT; Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Fitness to Practise Explained: What New Doctors Need to Know; GMC Regulation of Physician Associates: What Doctors Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Menopause Management in the UKMLA: What You Need to Know; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Palliative Care and End-of-Life Decisions in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Substance Misuse and Addiction in the UKMLA: What to Revise; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs PLAB: What Is the Difference?; Urology in the UKMLA: High-Yield Topics for the AKT; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus; Domestic Abuse and Adult Safeguarding in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
+          <t>Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>/news#psychiatry-communication-cpsa-stations</t>
+          <t>/news#pharmacology-prescribing-safety-ukmla</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -4761,41 +4761,41 @@
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Domestic Abuse and Adult Safeguarding in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Care of the Elderly and Frailty in the UKMLA: What to Revise; Chronic Pain Management in the UKMLA: What to Revise; Immunology and Allergy in the UKMLA: High-Yield Revision; Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide; Public Health and Screening in the UKMLA: What You Need to Know; Substance Misuse and Addiction in the UKMLA: What to Revise; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; UKMLA AKT Pass Mark and Pass Rate Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Public Health and Screening in the UKMLA: What You Need to Know</t>
+          <t>PLAB 2 Preparation: How to Excel in the Clinical Assessment</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>/news#public-health-and-screening-ukmla</t>
+          <t>/news#plab-2-preparation-guide</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -4804,41 +4804,41 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Medical Statistics and Evidence-Based Medicine in the UKMLA</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Resits: Rules, Limits, and How to Bounce Back</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; Care of the Elderly and Frailty in the UKMLA: What to Revise; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Medical Statistics and Evidence-Based Medicine in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Appeals and Resits; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Good Medical Practice and the UKMLA: What the GMC Expects; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; The Role of Mock Exams in UKMLA Preparation; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>UKMLA vs PLAB</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Radiology and Imaging Interpretation in the AKT</t>
+          <t>Prescribing in Renal and Hepatic Impairment: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>/news#radiology-imaging-akt-ukmla</t>
+          <t>/news#prescribing-in-renal-and-hepatic-impairment-ukmla</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Medically Unexplained Symptoms in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>MLA Content Map / Syllabus; Domestic Abuse and Adult Safeguarding in the UKMLA; Medically Unexplained Symptoms in the UKMLA: What to Revise; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Relocating to the UK: A Practical Guide for IMG Doctors</t>
+          <t>Psychiatry Communication Stations: Handling Difficult Conversations</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>/news#relocating-to-the-uk-a-practical-guide-for-img-doctors</t>
+          <t>/news#psychiatry-communication-cpsa-stations</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -4890,41 +4890,41 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; How to Write an NHS CV and Application That Gets Shortlisted; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Breaking Bad News in the CPSA: A Complete Guide; Consent and Mental Capacity in the UKMLA: The Complete Guide; Contraception Counselling in the UKMLA: A Complete Revision Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Domestic Abuse and Adult Safeguarding in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Read an AKT Stem: Avoiding Common Traps; Medically Unexplained Symptoms in the UKMLA: What to Revise; Menopause Management in the UKMLA: What You Need to Know; Mental Health Presentations in the UKMLA: What to Revise; The Role of Mock Exams in UKMLA Preparation; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Safeguarding Adults and Children: A UKMLA Revision Guide; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Public Health and Screening in the UKMLA: What You Need to Know</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>/news#respiratory-medicine-ukmla-revision</t>
+          <t>/news#public-health-and-screening-ukmla</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -4933,19 +4933,19 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>8</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
+          <t>Care of the Elderly and Frailty in the UKMLA: What to Revise; Medical Statistics and Evidence-Based Medicine in the UKMLA</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Preparation; MLA Content Map / Syllabus; Care of the Elderly and Frailty in the UKMLA: What to Revise; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Medical Statistics and Evidence-Based Medicine in the UKMLA; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
+          <t>Radiology and Imaging Interpretation in the AKT</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>/news#returning-to-practise-in-gulf-countries-dataflow-guide</t>
+          <t>/news#radiology-imaging-akt-ukmla</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -4976,41 +4976,41 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>AKT Exam Pattern; Preparation; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
+          <t>Relocating to the UK: A Practical Guide for IMG Doctors</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>/news#rheumatology-ukmla-revision</t>
+          <t>/news#relocating-to-the-uk-a-practical-guide-for-img-doctors</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5019,41 +5019,41 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Immunology and Allergy in the UKMLA: High-Yield Revision; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; How to Write an NHS CV and Application That Gets Shortlisted; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; UKMLA for Ethiopian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Ghanaian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Malaysian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Zimbabwean Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>Eligibility; Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; NHS Job Interview Preparation: A Complete Guide for IMGs and UK Graduates; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
+          <t>Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>/news#safeguarding-ukmla-revision</t>
+          <t>/news#respiratory-medicine-ukmla-revision</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5062,37 +5062,41 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Domestic Abuse and Adult Safeguarding in the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Clinical Examination Stations in the CPSA: A Practical Guide; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Radiology and Imaging Interpretation in the AKT; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Professional Practice &amp; Safety</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
+          <t>Clinical Systems Revision</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>MLA Content Map / Syllabus</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
+          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>/news#scotland-wales-northern-ireland-registration-differences</t>
+          <t>/news#returning-to-practise-in-gulf-countries-dataflow-guide</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5100,42 +5104,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D111" s="4" t="n">
-        <v>1</v>
+      <c r="D111" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>Understanding NHS Pay Scales and Banding for Doctors</t>
+          <t>UKMLA After MBBS in India: What to Do Next; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Official Resources; Registration Guide; The GMC Annual Retention Fee, Explained; GMC Registration Requirements for International Doctors: The Complete Process; The GMC Revalidation Process, Explained for New Doctors; Relocating to the UK: A Practical Guide for IMG Doctors; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
+          <t>Eligibility; Registration Guide; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How Long Does GMC Registration Take? A Realistic Timeline; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
+          <t>Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>/news#sepsis-recognition-and-management-ukmla</t>
+          <t>/news#rheumatology-ukmla-revision</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5144,19 +5148,19 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Genetics and Genomics in the UKMLA: What You Need to Know; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers</t>
+          <t>Dermatology in the UKMLA: Rashes, Lesions, and What to Know; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Immunology and Allergy in the UKMLA: High-Yield Revision; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Genetics and Genomics in the UKMLA: What You Need to Know; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Cardiology High-Yield Topics for the UKMLA AKT; Gastroenterology and Hepatology in the UKMLA AKT; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -5173,12 +5177,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
+          <t>Safeguarding Adults and Children: A UKMLA Revision Guide</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>/news#social-determinants-health-ukmla</t>
+          <t>/news#safeguarding-ukmla-revision</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5187,41 +5191,37 @@
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Public Health and Screening in the UKMLA: What You Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Domestic Abuse and Adult Safeguarding in the UKMLA; How to Read an AKT Stem: Avoiding Common Traps; MLA Content Map: The Blueprint Behind Every UKMLA Question; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Psychiatry Communication Stations: Handling Difficult Conversations; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; NICE Guidelines and the AKT: What You Actually Need to Know; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>MLA Content Map / Syllabus</t>
-        </is>
-      </c>
+          <t>Professional Practice &amp; Safety</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Substance Misuse and Addiction in the UKMLA: What to Revise</t>
+          <t>Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>/news#substance-misuse-and-addiction-ukmla</t>
+          <t>/news#scotland-wales-northern-ireland-registration-differences</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5229,42 +5229,42 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
-        <v>2</v>
+      <c r="D114" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
+          <t>Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; MLA Content Map / Syllabus; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Mental Health Presentations in the UKMLA: What to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management</t>
+          <t>Eligibility; Official Resources; Registration Guide; The GMC Annual Retention Fee, Explained; GMC Registration Requirements for International Doctors: The Complete Process; The GMC Revalidation Process, Explained for New Doctors; Relocating to the UK: A Practical Guide for IMG Doctors; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
+          <t>Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>/news#surgical-presentations-ukmla-revision</t>
+          <t>/news#sepsis-recognition-and-management-ukmla</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -5273,19 +5273,19 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT</t>
+          <t>Genetics and Genomics in the UKMLA: What You Need to Know; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Genetics and Genomics in the UKMLA: What You Need to Know; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
+          <t>Social Determinants of Health in the UKMLA: Person-Centred Care</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>/news#three-months-ukmla-akt-countdown</t>
+          <t>/news#social-determinants-health-ukmla</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5316,41 +5316,41 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E116" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E116" s="2" t="n">
-        <v>24</v>
-      </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>MLA Content Map: The Blueprint Behind Every UKMLA Question; Public Health and Screening in the UKMLA: What You Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; Transgender Health in the UKMLA: What the Content Map Covers; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
+          <t>Substance Misuse and Addiction in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>/news#time-management-akt-ukmla</t>
+          <t>/news#substance-misuse-and-addiction-ukmla</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -5359,41 +5359,41 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Nutrition and Metabolic Disorders in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; MLA Content Map / Syllabus; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Mental Health Presentations in the UKMLA: What to Revise; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management</t>
+          <t>Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>/news#toxicology-and-poisoning-ukmla</t>
+          <t>/news#surgical-presentations-ukmla-revision</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5402,19 +5402,19 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Substance Misuse and Addiction in the UKMLA: What to Revise</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; What Is an Angoff Standard Setting and Why Does It Matter?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Emergency Medicine and Acute Presentations in the UKMLA; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Gynaecological Cancers in the UKMLA: Red Flags and Referral; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; MLA Content Map: The Blueprint Behind Every UKMLA Question; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Three Months to the UKMLA AKT: A Final Preparation Countdown; Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
+          <t>Preparation; MLA Content Map / Syllabus; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Transgender Health in the UKMLA: What the Content Map Covers</t>
+          <t>Three Months to the UKMLA AKT: A Final Preparation Countdown</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>/news#transgender-health-in-the-ukmla</t>
+          <t>/news#three-months-ukmla-akt-countdown</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -5445,41 +5445,41 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Genetics and Genomics in the UKMLA: What You Need to Know; Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; Mental Health Presentations in the UKMLA: What to Revise; Paediatrics in the AKT and CPSA: A Focused Revision Guide; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Preparation for IMG Candidates: A Tailored Guide; How to Prepare for the UKMLA as a UK Final-Year Student; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; MLA Content Map / Syllabus; Consent and Mental Capacity in the UKMLA: The Complete Guide; Genetics and Genomics in the UKMLA: What You Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Preparation; MLA Content Map / Syllabus; Cardiology High-Yield Topics for the UKMLA AKT; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; Haematology in the UKMLA: Anaemia, Clotting, and Blood Cancers; How to Read an AKT Stem: Avoiding Common Traps; Infection and Microbiology in the UKMLA: Antibiotic Stewardship and More; Nephrology in the UKMLA: AKI, CKD, and Electrolyte Disorders; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Paediatrics in the AKT and CPSA: A Focused Revision Guide; Palliative Care and End-of-Life Decisions in the UKMLA; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management</t>
+          <t>Time Management in the UKMLA AKT: Strategies That Work</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>/news#trauma-and-orthopaedics-ukmla</t>
+          <t>/news#time-management-akt-ukmla</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5488,41 +5488,41 @@
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Urology in the UKMLA: High-Yield Topics for the AKT</t>
+          <t>Blood Tests and Investigations in the AKT: Data Interpretation Guide; Critical Care Basics in the UKMLA: Recognising the Deteriorating Patient; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; PLAB 2 Preparation: How to Excel in the Clinical Assessment; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Urology in the UKMLA: High-Yield Topics for the AKT</t>
+          <t>Appeals and Resits; AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; UKMLA vs PLAB; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Gastroenterology and Hepatology in the UKMLA AKT; How to Read an AKT Stem: Avoiding Common Traps; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Clinical Systems Revision</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>MLA Content Map / Syllabus</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>Toxicology and Poisoning in the UKMLA: High-Yield Overdose Management</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>/news#types-of-gmc-registration-explained</t>
+          <t>/news#toxicology-and-poisoning-ukmla</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -5531,41 +5531,41 @@
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>The Certificate of Completion of Training (CCT), Explained; The GMC Annual Retention Fee, Explained; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Substance Misuse and Addiction in the UKMLA: What to Revise</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>AKT Exam Pattern; Preparation; MLA Content Map / Syllabus; Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Emergency Medicine and Acute Presentations in the UKMLA; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
+          <t>Transgender Health in the UKMLA: What the Content Map Covers</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
+          <t>/news#transgender-health-in-the-ukmla</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -5574,41 +5574,41 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The NHS Pension Scheme for Doctors, Explained; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
+          <t>Consent and Mental Capacity in the UKMLA: The Complete Guide; Genetics and Genomics in the UKMLA: What You Need to Know; Sepsis Recognition and Management in the UKMLA: The Essential Guide</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Registration Guide; MLA Content Map / Syllabus; Consent and Mental Capacity in the UKMLA: The Complete Guide; Genetics and Genomics in the UKMLA: What You Need to Know; Good Medical Practice and the UKMLA: What the GMC Expects; Sepsis Recognition and Management in the UKMLA: The Essential Guide; Social Determinants of Health in the UKMLA: Person-Centred Care; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
+          <t>Trauma and Orthopaedics in the UKMLA: High-Yield Fracture Management</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-medical-schools-ukmla-implementation</t>
+          <t>/news#trauma-and-orthopaedics-ukmla</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -5617,41 +5617,41 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>AKT Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; What Is the UKMLA?; Anaesthesia and Perioperative Medicine in the UKMLA: A Foundation Doctor's Guide; Radiology and Imaging Interpretation in the AKT; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Urology in the UKMLA: High-Yield Topics for the AKT</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>Clinical Systems Revision</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>What Is the UKMLA?</t>
+          <t>MLA Content Map / Syllabus</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
+          <t>Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-guide-for-international-doctors</t>
+          <t>/news#types-of-gmc-registration-explained</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -5660,41 +5660,41 @@
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Indemnity Insurance for Doctors, Explained; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support</t>
+          <t>The Certificate of Completion of Training (CCT), Explained; Cost of GMC Registration 2026: Full Fee Breakdown; The GMC Annual Retention Fee, Explained; GMC EPIC/MyIntealth Verification Process Explained; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Practising Medicine in Scotland, Wales and Northern Ireland: What's Different?; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Registration Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC Registration Requirements for International Doctors: The Complete Process; The GMC Revalidation Process, Explained for New Doctors; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
+          <t>UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
+          <t>/news#uk-doctor-salary-guide-for-indian-doctors</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -5703,19 +5703,19 @@
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Locum vs Substantive NHS Posts: Which Is Right for You?; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; OET vs IELTS for GMC Registration: Which Should You Take?</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; The Medical Training Prioritisation Act 2026: What It Means for IMGs; The NHS Pension Scheme for Doctors, Explained; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Zimbabwean Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; Understanding NHS Pay Scales and Banding for Doctors</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>Eligibility; Fees; Results and Scoring; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -5732,12 +5732,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
+          <t>How UK Medical Schools Implement the UKMLA: An Overview</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-format-preparation</t>
+          <t>/news#uk-medical-schools-ukmla-implementation</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -5746,41 +5746,41 @@
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>What Is an Angoff Standard Setting and Why Does It Matter?; Clinical Examination Stations in the CPSA: A Practical Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Read an AKT Stem: Avoiding Common Traps; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; MBBS in UK for Indian Students: Costs, Entry Routes and How It Differs From the IMG Path; Mental Health Presentations in the UKMLA: What to Revise; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA Eligibility: Who Can Sit the Exam?; The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA Results: How to Interpret Your Feedback Report; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map; UKMLA vs PLAB: What Is the Difference?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; How to Read an AKT Stem: Avoiding Common Traps; Respiratory Medicine for the UKMLA: What to Focus On; Surgical Presentations in the UKMLA: What a Foundation Doctor Needs to Know; Time Management in the UKMLA AKT: Strategies That Work; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA CPSA: What the Clinical Exam Really Tests; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>What Is the UKMLA?</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
+          <t>UK Visa Guide for International Doctors: Health and Care Worker Visa Explained</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
+          <t>/news#uk-visa-guide-for-international-doctors</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -5789,41 +5789,41 @@
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>How to Pass the UKMLA on Your First Attempt; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Indemnity Insurance for Doctors, Explained; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA for Ethiopian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Ghanaian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Malaysian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Zimbabwean Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Results and Scoring; What Is an Angoff Standard Setting and Why Does It Matter?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
+          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Results &amp; Scoring</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
         <is>
-          <t>Results and Scoring</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+          <t>UK Visa Salary Threshold Changes 2026: What Doctors Need to Know</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-akt-test-centres-guide</t>
+          <t>/news#uk-visa-salary-threshold-changes-2026-for-doctors</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -5832,19 +5832,19 @@
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Bringing Your Family to the UK: A Dependant Visa Guide for Doctors; GMC Order Reform 2026: The Consultation on Protected Medical Titles; Locum vs Substantive NHS Posts: Which Is Right for You?; Medical Training Initiative Scheme Closure 2026: What IMGs Need to Know; The Medical Training Prioritisation Act 2026: What It Means for IMGs; OET vs IELTS for GMC Registration: Which Should You Take?</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Eligibility; Fees; GMC Order Reform 2026: The Consultation on Protected Medical Titles; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -5854,19 +5854,19 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
+          <t>UKMLA After MBBS in India: What to Do Next</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-and-academic-foundation-programme</t>
+          <t>/news#ukmla-after-mbbs-in-india</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -5878,21 +5878,21 @@
         <v>2</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; What Is the UKMLA?; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
+          <t>Eligibility; Preparation; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Core UKMLA Overview</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
+          <t>UKMLA AKT: Format, Question Types, and How to Prepare</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
+          <t>/news#ukmla-akt-format-preparation</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -5918,41 +5918,41 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Pass the UKMLA on Your First Attempt; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Radiology and Imaging Interpretation in the AKT; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Pass Mark and Pass Rate Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Preparation; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>Appeals and Resits; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Blood Tests and Investigations in the AKT: Data Interpretation Guide; Dermatology in the UKMLA: Rashes, Lesions, and What to Know; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Endocrinology and Diabetes in the UKMLA: A Targeted Revision Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; Gastroenterology and Hepatology in the UKMLA AKT; Good Medical Practice and the UKMLA: What the GMC Expects; How to Read an AKT Stem: Avoiding Common Traps; Neurology in the UKMLA: High-Yield Topics and Revision Tips; NICE Guidelines and the AKT: What You Actually Need to Know; Obstetrics and Gynaecology in the UKMLA: Key Topics to Revise; Ophthalmology and ENT in the UKMLA: What Foundation Doctors Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Radiology and Imaging Interpretation in the AKT; Respiratory Medicine for the UKMLA: What to Focus On; Safeguarding Adults and Children: A UKMLA Revision Guide; Time Management in the UKMLA AKT: Strategies That Work; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Results: How to Interpret Your Feedback Report; What Is the UKMLA? A Complete Beginner's Guide</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Exam Preparation</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
+          <t>UKMLA AKT Pass Mark and Pass Rate Explained</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-cpsa-what-it-tests</t>
+          <t>/news#ukmla-akt-pass-mark-and-pass-rate-explained</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -5961,41 +5961,41 @@
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>Breaking Bad News in the CPSA: A Complete Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; How to Pass the UKMLA on Your First Attempt; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>Appeals and Resits; Results and Scoring; What Is an Angoff Standard Setting and Why Does It Matter?; Managing UKMLA Exam Anxiety: Practical Strategies for Candidates; MLA Content Map: The Blueprint Behind Every UKMLA Question; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA Results: How to Interpret Your Feedback Report; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Exam Format</t>
+          <t>Results &amp; Scoring</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>CPSA Exam Pattern</t>
+          <t>Results and Scoring</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-crash-course-for-doctors</t>
+          <t>/news#ukmla-akt-test-centres-guide</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6004,19 +6004,19 @@
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>Preparation; MLA Content Map / Syllabus; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT: Format, Question Types, and How to Prepare; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -6026,19 +6026,19 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Preparation</t>
+          <t>AKT Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
+          <t>UKMLA and the Academic Foundation Programme: What Research-Minded Students Need to Know</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-eligibility-who-can-sit</t>
+          <t>/news#ukmla-and-academic-foundation-programme</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -6047,24 +6047,24 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Foundation Programme 2026 Recruitment Changes: What's New for Applicants; How to Prepare for the UKMLA as a UK Final-Year Student; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Eligibility; Registration Guide; What Is the UKMLA?; Foundation Programme 2026 Recruitment Changes: What's New for Applicants; Understanding the Foundation Programme: What Awaits After the UKMLA; Three Months to the UKMLA AKT: A Final Preparation Countdown; Time Management in the UKMLA AKT: Strategies That Work; UKMLA for Graduate-Entry Medical Students: What Is Different?; What Happens If You Fail the UKMLA? The Impact on Your Foundation Year</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Core UKMLA Overview</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -6076,12 +6076,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
+          <t>UKMLA Anki Deck and Flashcard Revision: The Complete Guide</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exam-booking-process-gmc-online</t>
+          <t>/news#ukmla-anki-deck-and-flashcard-revision-guide</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6090,41 +6090,41 @@
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; How to Pass the UKMLA on Your First Attempt; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
+          <t>Eligibility; Preparation; Group Study vs Solo Study for the UKMLA: What Works Best?; How to Pass the UKMLA on Your First Attempt; MLA Content Map: The Blueprint Behind Every UKMLA Question; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; How to Write UKMLA Revision Notes That Actually Work; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Exam Preparation</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Day: What to Expect at the AKT and CPSA</t>
+          <t>UKMLA CPSA: What the Clinical Exam Really Tests</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exam-day-what-to-expect</t>
+          <t>/news#ukmla-cpsa-what-it-tests</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -6133,37 +6133,41 @@
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>The History of the UKMLA and PLAB Transition, Explained; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr"/>
+          <t>Breaking Bad News in the CPSA: A Complete Guide; Mental Health Presentations in the UKMLA: What to Revise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide; What Is the UKMLA? A Complete Beginner's Guide</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Preparation; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; What Is the UKMLA?; Cardiology High-Yield Topics for the UKMLA AKT; Clinical Examination Stations in the CPSA: A Practical Guide; ECG Interpretation for the UKMLA: The Findings You Must Recognise; Neurology in the UKMLA: High-Yield Topics and Revision Tips; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; PLAB 2 Preparation: How to Excel in the Clinical Assessment; Psychiatry Communication Stations: Handling Difficult Conversations; Respiratory Medicine for the UKMLA: What to Focus On; Rheumatology in the UKMLA: Joints, Inflammation, and Autoimmunity; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>Exam Format</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Registration Guide</t>
+          <t>CPSA Exam Pattern</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
+          <t>UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
+          <t>/news#ukmla-crash-course-for-doctors</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6172,41 +6176,41 @@
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Types of GMC Registration Explained: Provisional, Full, Specialist and GP</t>
+          <t>Best Question Bank for UKMLA: The 2026 Head-to-Head Comparison; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Preparation; MLA Content Map / Syllabus; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Pass the UKMLA on Your First Attempt; The Role of Mock Exams in UKMLA Preparation; Three Months to the UKMLA AKT: A Final Preparation Countdown; UKMLA Anki Deck and Flashcard Revision: The Complete Guide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Syllabus 2026 Changes: What's New in the Updated MLA Content Map</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Registration &amp; Eligibility</t>
+          <t>IMG Country Routes &amp; Global Comparisons</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Preparation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
+          <t>UKMLA Eligibility: Who Can Sit the Exam?</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-explained</t>
+          <t>/news#ukmla-eligibility-who-can-sit</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -6215,19 +6219,19 @@
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
+          <t>GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; What Is the UKMLA?; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; Understanding the Foundation Programme: What Awaits After the UKMLA; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA for Graduate-Entry Medical Students: What Is Different?; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -6237,19 +6241,19 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
+          <t>The UKMLA Exam Booking Process: A Step-by-Step Walkthrough</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-fees-for-img-2026</t>
+          <t>/news#ukmla-exam-booking-process-gmc-online</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6258,19 +6262,19 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>The GMC Annual Retention Fee, Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; Is UKMLA Replacing PLAB? The Real Relationship, Explained; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>AKT Exam Pattern; CPSA Exam Pattern; Key Dates; Registration Guide; Disability, Access, and Inclusion in the UKMLA: A Candidate's Guide; GMC Welcome to UK Practice: A Guide to the Free Induction Workshop; How to Register for PLAB 1: A Step-by-Step Guide for IMGs; Is UKMLA Replacing PLAB? The Real Relationship, Explained; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -6280,19 +6284,19 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA Exam Day: What to Expect at the AKT and CPSA</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-bangladeshi-doctors</t>
+          <t>/news#ukmla-exam-day-what-to-expect</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -6301,41 +6305,37 @@
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
-        </is>
-      </c>
-      <c r="G139" s="3" t="inlineStr">
-        <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
-        </is>
-      </c>
+          <t>The History of the UKMLA and PLAB Transition, Explained; UKMLA Special Circumstances: Accommodations Beyond Disability Access</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Registration Guide</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-chinese-doctors</t>
+          <t>/news#ukmla-exemptions-for-specialist-and-gp-doctors</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -6344,24 +6344,24 @@
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Foundation Year vs Specialty Training for IMGs: Which Route After the UKMLA?; GMC Order Reform 2026: The Consultation on Protected Medical Titles; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Internship Requirement for GMC Registration, Explained; Joining a Royal College After the UKMLA: MRCP, MRCS and MRCGP Explained; Locally Employed Doctors: The Route to Full and Specialist GMC Registration; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; Types of GMC Registration Explained: Provisional, Full, Specialist and GP; UKMLA After MBBS in India: What to Do Next</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Eligibility; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; Pharmacology and Prescribing Safety in the UKMLA: A Revision Guide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA Fees: The Complete 2026 Cost Breakdown</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-egyptian-doctors</t>
+          <t>/news#ukmla-fees-explained</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -6387,41 +6387,41 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Results: How to Interpret Your Feedback Report</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; Results and Scoring; MLA Content Map / Syllabus; UKMLA vs PLAB; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Preparation for IMG Candidates: A Tailored Guide</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-filipino-doctors</t>
+          <t>/news#ukmla-fees-for-img-2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -6430,41 +6430,41 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Cost of GMC Registration 2026: Full Fee Breakdown; The GMC Annual Retention Fee, Explained; GMC Registration Refund Policy: When You Can (and Can't) Get Your Fee Back; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Salary Threshold Changes 2026: What Doctors Need to Know; UKMLA Crash Course for Doctors: How to Choose the Right Intensive Course; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Indian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA vs AMC and MCCQE: Comparing the UK Route to Australia and Canada; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Cost of GMC Registration 2026: Full Fee Breakdown; How to Become a Doctor in the UK from India: The Complete UKMLA Route; The Role of Mock Exams in UKMLA Preparation; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Key Dates and Sitting Schedule: What to Know; UKMLA Preparation for IMG Candidates: A Tailored Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA Resits: Rules, Limits, and How to Bounce Back; UKMLA vs NEET PG: Which Path Should Indian Medical Graduates Choose?; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>IMG Country Routes &amp; Global Comparisons</t>
+          <t>Registration &amp; Eligibility</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>Eligibility</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-gulf-doctors</t>
+          <t>/news#ukmla-for-bangladeshi-doctors</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -6473,19 +6473,19 @@
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Nepali Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; UKMLA vs PLAB; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; Is an Indian MBBS Valid in the UK? UKMLA Recognition and Degree Validity Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Nepali Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA for Sri Lankan Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -6502,12 +6502,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference</t>
+          <t>UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-international-medical-graduates-country-routes</t>
+          <t>/news#ukmla-for-chinese-doctors</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -6516,19 +6516,19 @@
         </is>
       </c>
       <c r="D144" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E144" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; The Medical Training Prioritisation Act 2026: What It Means for IMGs; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Registration Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>Eligibility; Registration Guide; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; OET vs IELTS for GMC Registration: Which Should You Take?; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Jamaican and Trinidadian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-jamaican-and-trinidadian-doctors</t>
+          <t>/news#ukmla-for-egyptian-doctors</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -6559,19 +6559,19 @@
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Sudanese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Registration Guide; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration for EU and Irish Doctors: What Changed After Brexit; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA for Pakistani Doctors: Eligibility, Fees and the Route to Practising in the UK; UKMLA vs USMLE: Which Exam Is Easier, Cheaper and Better for Your Career?</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Jordanian and Iraqi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Ethiopian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-jordanian-and-iraqi-doctors</t>
+          <t>/news#ukmla-for-ethiopian-doctors</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -6601,20 +6601,20 @@
           <t>Blog Post</t>
         </is>
       </c>
-      <c r="D146" s="4" t="n">
-        <v>1</v>
+      <c r="D146" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E146" s="2" t="n">
         <v>10</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
+          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Sudanese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>Eligibility; Fees; Registration Guide; English Language Requirements for the UKMLA: IELTS and OET Scores Explained; Which Medical Qualifications Does the GMC Accept? PMQ Recognition Explained; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Gulf and Saudi Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>Eligibility; Fees; GMC EPIC/MyIntealth Verification Process Explained; GMC Registration Requirements for International Doctors: The Complete Process; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Refugee Doctors: The GMC Assistance Programme and Fee Support; UKMLA for Sudanese Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -6631,12 +6631,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration</t>
+          <t>UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-kenyan-and-east-african-doctors</t>
+          <t>/news#ukmla-for-filipino-doctors</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -6645,19 +6645,19 @@
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>GMC Registration for EU and Irish Doctors: What Changed After Brexit; Returning to Practise in Gulf Countries: The DataFlow Verification Guide</t>
+          <t>GMC English Language Exemption: Do You Need to Sit IELTS or OET?; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UKMLA for Chinese Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Malaysian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Vietnamese and Indonesian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; GMC English Language Exemption: Do You Need to Sit IELTS or OET?; GMC Registration for EU and Irish Doctors: What Changed After Brexit; MLA Content Map: The Blueprint Behind Every UKMLA Question; Psychiatry Communication Stations: Handling Difficult Conversations; Returning to Practise in Gulf Countries: The DataFlow Verification Guide; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Eligibility; AKT Exam Pattern; Registration Guide; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK from India: The Complete UKMLA Route; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Malaysian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
+          <t>UKMLA for Ghanaian Doctors: Eligibility, Fees and the Route to GMC Registration</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>/news#ukmla-for-nigerian-doctors</t>
+          <t>/news#ukmla-for-ghanaian-doctors</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -6688,19 +6688,19 @@
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>English Language Requirements for the UKMLA: IELTS and OET Scores Explained; GMC Registration and EPIC Verification for Doctors From India: A Step-by-Step Guide; GMC Registration Requirements for International Doctors: The Complete Process; How to Become a Doctor in the UK: The Complete GMC Registration Guide for IMGs; UK Doctor Salary for Indian Doctors: NHS Pay Scales and What You'll Actually Take Home; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA AKT Test Centres: Where You Can Sit the Exam in India, Pakistan, the UK and Worldwide; Do Experienced Doctors Need to Take the UKMLA? Exemptions for Specialists and GPs; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA for Bangladeshi Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Egyptian Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for Filipino Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Kenyan and East African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA for South African Doctors: Eligibility, Fees and the Route to GMC Registration; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources; UKMLA to NHS Job: What Happens After You Pass and Register With the GMC</t>
+          <t>UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nigerian Doctors: Eligibility, Fees and How to Register with the GMC</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>Appeals and Resits; Eligibility; AKT Exam Pattern; CPSA Exam Pattern; Fees; Key Dates; Official Resources; Preparation; Registration Guide; MLA Content Map / Syllabus; UKMLA vs PLAB; Emergency Medicine and Acute Presentations in the UKMLA; Understanding the Foundation Programme: What Awaits After the UKMLA; How to Become a Doctor in the UK from India: The Complete UKMLA Route; MLA Content Map: The Blueprint Behind Every UKMLA Question; NICE Guidelines and the AKT: What You Actually Need to Know; Patient Safety in the UKMLA: Prescribing Errors and Near-Miss Reporting; Psychiatry Communication Stations: Handling Difficult Conversations; Social Determinants of Health in the UKMLA: Person-Centred Care; How UK Medical Schools Implement the UKMLA: An Overview; UKMLA Eligibility: Who Can Sit the Exam?; UKMLA Fees: The Complete 2026 Cost Breakdown; UKMLA Exam Fees for International Medical Graduates: 2026 Cost Guide; UKMLA Question Bank and Mock Tests: The Complete Guide to Practice Resources</t>
+          <t>Eligibility; Fees; GMC EPIC/MyIntealth Verification Process Explained; GMC Registration Requirements for International Doctors: The Complete Process; Relocating to the UK: A Practical Guide for IMG Doctors; UK Visa Guide for International Doctors: Health and Care Worker Visa Explained; UKMLA for International Medical Graduates: Country-by-Country Quick Reference; UKMLA for Nig